--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -9083,7 +9083,7 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Jerry，侧面向右跑；真人原型需本人同意</t>
+          <t>Datto，侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -9945,22 +9945,22 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>3 个 Boss 波每局从 6 位传奇跑者里随机抽：Nox（九命复活）、Aurum（召唤金甲跑者）、Slimo（黏液加速）、Rocco（铁头冲刺）、Chuckles（大笑让装置停工）、Jerry（对常用装置产生抗性）。</t>
+          <t>3 个 Boss 波每局从 6 位传奇跑者里随机抽：Nox（九命复活）、Aurum（召唤金甲跑者）、Slimo（黏液加速）、Rocco（铁头冲刺）、Chuckles（大笑让装置停工）、Datto（对常用装置产生抗性）。</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>3 个 Boss 波每局从 6 位传奇跑者里随机抽：Nox（九命复活）、Aurum（召唤金甲跑者）、Slimo（黏液加速）、Rocco（铁头冲刺）、Chuckles（大笑让装置停工）、Jerry（对常用装置产生抗性）。</t>
+          <t>3 个 Boss 波每局从 6 位传奇跑者里随机抽：Nox（九命复活）、Aurum（召唤金甲跑者）、Slimo（黏液加速）、Rocco（铁头冲刺）、Chuckles（大笑让装置停工）、Datto（对常用装置产生抗性）。</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Each run draws 3 bosses from 6 legendary runners: Nox (nine lives), Aurum (summons golden runners), Slimo (slime boost), Rocco (headstrong dash), Chuckles (laughter jams devices), Jerry (adapts to your most-used device).</t>
+          <t>Each run draws 3 bosses from 6 legendary runners: Nox (nine lives), Aurum (summons golden runners), Slimo (slime boost), Rocco (headstrong dash), Chuckles (laughter jams devices), Datto (adapts to your most-used device).</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Chaque partie tire 3 boss parmi 6 coureurs légendaires : Nox (neuf vies), Aurum (invoque des coureurs dorés), Slimo (bave accélérante), Rocco (charge tête baissée), Chuckles (son rire bloque les dispositifs), Jerry (s’adapte à ton dispositif favori).</t>
+          <t>Chaque partie tire 3 boss parmi 6 coureurs légendaires : Nox (neuf vies), Aurum (invoque des coureurs dorés), Slimo (bave accélérante), Rocco (charge tête baissée), Chuckles (son rire bloque les dispositifs), Datto (s’adapte à ton dispositif favori).</t>
         </is>
       </c>
     </row>
@@ -24145,7 +24145,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>Datto</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -10213,7 +10213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D274"/>
+  <dimension ref="A1:D275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -16206,8 +16206,30 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="10" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>再点一次离开（本局进度不保存）</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>再点一次离开（本局进度不保存）</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>Tap again to leave (this run is not saved)</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="inlineStr">
+        <is>
+          <t>Touche encore pour quitter (partie non sauvegardée)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="10" t="inlineStr">
         <is>
           <t>※ 花括号里的 {n}、{x} 等是占位符，翻译时要原样保留。</t>
         </is>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -7671,10 +7671,18 @@
           <t>P1 样板关</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.png</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.json</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>50</v>
@@ -10464,13 +10472,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.png</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.json</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I66" s="7" t="n">
         <v>0.5</v>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -7607,10 +7607,18 @@
           <t>P1 样板关</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.png</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.json</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>50</v>
@@ -10400,13 +10408,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.png</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.json</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I66" s="7" t="n">
         <v>0.5</v>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -1039,7 +1039,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>地图：每种跑道的路线点和装置空位坐标</t>
+          <t>地图：每种跑道的路线点（空位坐标已不再使用：装置可以放在跑道外任意空格子上）</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1618,7 +1618,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>pad</t>
+          <t>freeup</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -1639,50 +1639,46 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>额外放置点</t>
+          <t>鞋匠</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Extra Spot</t>
+          <t>Cobbler</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Emplacement bonus</t>
+          <t>Cordonnier</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>获得 1 个放置点：点地图上跑道以外的空地，新增一个装置空位</t>
+          <t>场上一个装置沿主路线免费升 1 级（没有装置时改为 +100 GST）</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>Gain 1 spot: tap open ground off the track to add a new device spot</t>
+          <t>One device gets a free tier on its main path (+100 GST if you have none)</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Gagne 1 emplacement : touche un terrain libre hors de la piste pour créer un emplacement</t>
+          <t>Un dispositif gagne un niveau gratuit sur sa voie principale (+100 GST si aucun)</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>v1 = 放置点个数</t>
-        </is>
-      </c>
+      <c r="N9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>freeup</t>
+          <t>coupon</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -1703,46 +1699,50 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>鞋匠</t>
+          <t>升级卷轴</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Cobbler</t>
+          <t>Level-up Scroll</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Cordonnier</t>
+          <t>Parchemin d’amélioration</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>场上一个装置沿主路线免费升 1 级（没有装置时改为 +100 GST）</t>
+          <t>接下来 3 次路线升级半价</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>One device gets a free tier on its main path (+100 GST if you have none)</t>
+          <t>Next 3 path upgrades are half price</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Un dispositif gagne un niveau gratuit sur sa voie principale (+100 GST si aucun)</t>
+          <t>Les 3 prochaines améliorations à moitié prix</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="9" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>v1 = 半价次数</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>coupon</t>
+          <t>m_dart</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1750,63 +1750,63 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>道具</t>
+          <t>徽章</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>升级卷轴</t>
+          <t>（自动）</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Level-up Scroll</t>
+          <t>（自动）</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Parchemin d’amélioration</t>
+          <t>（自动）</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>接下来 3 次路线升级半价</t>
+          <t>（自动）</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>Next 3 path upgrades are half price</t>
+          <t>（自动）</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Les 3 prochaines améliorations à moitié prix</t>
+          <t>（自动）</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>v1 = 半价次数</t>
+          <t>名称和说明自动生成</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>m_dart</t>
+          <t>m_bomb</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
@@ -1870,7 +1870,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>m_bomb</t>
+          <t>m_frost</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -1934,7 +1934,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>m_frost</t>
+          <t>m_sniper</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
@@ -1998,7 +1998,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>m_sniper</t>
+          <t>m_tesla</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -2062,7 +2062,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>m_tesla</t>
+          <t>m_miner</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
@@ -2126,7 +2126,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>m_miner</t>
+          <t>m_lure</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -2190,7 +2190,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>m_lure</t>
+          <t>breaker</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>徽章</t>
+          <t>道具</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2211,50 +2211,50 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>（自动）</t>
+          <t>创世鞋</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>（自动）</t>
+          <t>Genesis Sneaker</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>（自动）</t>
+          <t>Sneaker Genesis</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>（自动）</t>
+          <t>6 级专精升级费用 −30%</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>（自动）</t>
+          <t>Tier-6 specialisation upgrades −30%</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>（自动）</t>
+          <t>Spécialisations de niveau 6 −30 %</t>
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>名称和说明自动生成</t>
+          <t>v1 = 费用倍率</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>breaker</t>
+          <t>drill</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -2262,63 +2262,63 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>道具</t>
+          <t>宝石</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>创世鞋</t>
+          <t>效率宝石</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Genesis Sneaker</t>
+          <t>Efficiency Gem</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Sneaker Genesis</t>
+          <t>Gemme d’efficacité</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>6 级专精升级费用 −30%</t>
+          <t>所有装置效果 +15%（可叠加）</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Tier-6 specialisation upgrades −30%</t>
+          <t>All devices +15% effect (stacks)</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Spécialisations de niveau 6 −30 %</t>
+          <t>Tous les dispositifs +15 % d’effet (cumulable)</t>
         </is>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>v1 = 费用倍率</t>
+          <t>v1 = 效果加成</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>drill</t>
+          <t>crit</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
@@ -2339,50 +2339,50 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>效率宝石</t>
+          <t>幸运宝石</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Efficiency Gem</t>
+          <t>Luck Gem</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Gemme d’efficacité</t>
+          <t>Gemme de chance</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>所有装置效果 +15%（可叠加）</t>
+          <t>暴击率 +10%（可叠加）</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>All devices +15% effect (stacks)</t>
+          <t>Crit chance +10% (stacks)</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Tous les dispositifs +15 % d’effet (cumulable)</t>
+          <t>Chance de critique +10 % (cumulable)</t>
         </is>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>v1 = 效果加成</t>
+          <t>v1 = 暴击率加成</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
@@ -2403,50 +2403,50 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>幸运宝石</t>
+          <t>舒适宝石</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Luck Gem</t>
+          <t>Comfort Gem</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Gemme de chance</t>
+          <t>Gemme de confort</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>暴击率 +10%（可叠加）</t>
+          <t>生命 +6</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Crit chance +10% (stacks)</t>
+          <t>Lives +6</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>Chance de critique +10 % (cumulable)</t>
+          <t>Vies +6</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>v1 = 暴击率加成</t>
+          <t>v1 = 生命</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>loot</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>宝石</t>
+          <t>道具</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -2467,50 +2467,50 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>舒适宝石</t>
+          <t>GST 红包</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Comfort Gem</t>
+          <t>GST Red Packet</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Gemme de confort</t>
+          <t>Enveloppe GST</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>生命 +6</t>
+          <t>立即获得 120 GST</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Lives +6</t>
+          <t>Get 120 GST now</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>Vies +6</t>
+          <t>Gagne 120 GST tout de suite</t>
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>v1 = 生命</t>
+          <t>v1 = GST</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>loot</t>
+          <t>golden</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
@@ -2527,54 +2527,54 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>GST 红包</t>
+          <t>神秘箱</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>GST Red Packet</t>
+          <t>Mystery Box</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Enveloppe GST</t>
+          <t>Mystery Box</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>立即获得 120 GST</t>
+          <t>10% 的对手跑者背着神秘箱，劝退后 GST ×5</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>Get 120 GST now</t>
+          <t>10% of rival runners carry a Mystery Box: GST ×5 when they quit</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>Gagne 120 GST tout de suite</t>
+          <t>10 % des coureurs rivaux portent une Mystery Box : GST ×5 à l’abandon</t>
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>v1 = GST</t>
+          <t>概率与倍率见全局</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>golden</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2595,32 +2595,32 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>神秘箱</t>
+          <t>GMT 质押</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Mystery Box</t>
+          <t>GMT Staking</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Mystery Box</t>
+          <t>Staking GMT</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>10% 的对手跑者背着神秘箱，劝退后 GST ×5</t>
+          <t>每波结束获得当前 GST 10% 的利息（最多 60）</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>10% of rival runners carry a Mystery Box: GST ×5 when they quit</t>
+          <t>After each wave, earn 10% interest on your GST (max 60)</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>10 % des coureurs rivaux portent une Mystery Box : GST ×5 à l’abandon</t>
+          <t>Après chaque vague, 10 % d’intérêts sur ton GST (max 60)</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>概率与倍率见全局</t>
+          <t>利率与上限见全局</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>bank</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
@@ -2659,32 +2659,32 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>GMT 质押</t>
+          <t>Gas Hero 毒气</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>GMT Staking</t>
+          <t>Gas Hero Gas</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Staking GMT</t>
+          <t>Gaz Gas Hero</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>每波结束获得当前 GST 10% 的利息（最多 60）</t>
+          <t>跑者退赛时喷出毒气，波及身边跑者，可以连锁</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>After each wave, earn 10% interest on your GST (max 60)</t>
+          <t>Runners who quit release gas that hits those nearby, and can chain</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>Après chaque vague, 10 % d’intérêts sur ton GST (max 60)</t>
+          <t>Les coureurs qui abandonnent libèrent un gaz qui touche les voisins, en chaîne</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>利率与上限见全局</t>
+          <t>数值见全局</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
@@ -2723,50 +2723,50 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Gas Hero 毒气</t>
+          <t>MOOAR 折扣</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Gas Hero Gas</t>
+          <t>MOOAR Discount</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Gaz Gas Hero</t>
+          <t>Remise MOOAR</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>跑者退赛时喷出毒气，波及身边跑者，可以连锁</t>
+          <t>放置和升级费用 −20%</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Runners who quit release gas that hits those nearby, and can chain</t>
+          <t>Placing and upgrading −20%</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>Les coureurs qui abandonnent libèrent un gaz qui touche les voisins, en chaîne</t>
+          <t>Placement et améliorations −20 %</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>数值见全局</t>
+          <t>v1 = 费用倍率</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>maniac</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
@@ -2787,50 +2787,50 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>MOOAR 折扣</t>
+          <t>连续打卡</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>MOOAR Discount</t>
+          <t>Check-in Streak</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Remise MOOAR</t>
+          <t>Série de check-ins</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>放置和升级费用 −20%</t>
+          <t>燃脂模式所需连续劝退 50 → 30</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>Placing and upgrading −20%</t>
+          <t>Fat-burn mode needs 30 stops instead of 50</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Placement et améliorations −20 %</t>
+          <t>Le mode brûle-graisse demande 30 arrêts au lieu de 50</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.8</v>
+        <v>30</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>v1 = 费用倍率</t>
+          <t>v1 = 所需连续劝退</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>maniac</t>
+          <t>devil</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>道具</t>
+          <t>交易</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -2851,50 +2851,50 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>连续打卡</t>
+          <t>GST 借贷</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Check-in Streak</t>
+          <t>GST Loan</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Série de check-ins</t>
+          <t>Prêt GST</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>燃脂模式所需连续劝退 50 → 30</t>
+          <t>立即生效：+250 GST；之后对手体力 +15%</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>Fat-burn mode needs 30 stops instead of 50</t>
+          <t>Instant: +250 GST; rivals get +15% stamina from now on</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>Le mode brûle-graisse demande 30 arrêts au lieu de 50</t>
+          <t>Immédiat : +250 GST ; les rivaux ont ensuite +15 % d’endurance</t>
         </is>
       </c>
       <c r="L28" s="7" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>v1 = 所需连续劝退</t>
+          <t>v1 = GST，v2 = 对手体力倍率</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>devil</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
@@ -2915,50 +2915,50 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>GST 借贷</t>
+          <t>透支生命</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>GST Loan</t>
+          <t>Overdraw Lives</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Prêt GST</t>
+          <t>Vies à découvert</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>立即生效：+250 GST；之后对手体力 +15%</t>
+          <t>立即生效：所有装置效果 +40%；生命 −10</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>Instant: +250 GST; rivals get +15% stamina from now on</t>
+          <t>Instant: all devices +40% effect; lives −10</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>Immédiat : +250 GST ; les rivaux ont ensuite +15 % d’endurance</t>
+          <t>Immédiat : tous les dispositifs +40 % d’effet ; vies −10</t>
         </is>
       </c>
       <c r="L29" s="7" t="n">
-        <v>250</v>
+        <v>0.4</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>v1 = GST，v2 = 对手体力倍率</t>
+          <t>v1 = 效果加成，v2 = 扣除生命</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>glass</t>
+          <t>track</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
@@ -2979,50 +2979,50 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>透支生命</t>
+          <t>牛市狂奔</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Overdraw Lives</t>
+          <t>Bull Run</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Vies à découvert</t>
+          <t>Bull run</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>立即生效：所有装置效果 +40%；生命 −10</t>
+          <t>立即生效：对手移速 +15%；劝退获得 GST +50%</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>Instant: all devices +40% effect; lives −10</t>
+          <t>Instant: rivals +15% speed; +50% GST per runner stopped</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>Immédiat : tous les dispositifs +40 % d’effet ; vies −10</t>
+          <t>Immédiat : rivaux +15 % de vitesse ; +50 % de GST par coureur arrêté</t>
         </is>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.4</v>
+        <v>1.15</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>v1 = 效果加成，v2 = 扣除生命</t>
+          <t>v1 = 对手速度倍率，v2 = GST 倍率</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>twin</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>交易</t>
+          <t>道具</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
@@ -3043,50 +3043,50 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>牛市狂奔</t>
+          <t>双倍铸造</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Bull Run</t>
+          <t>Double Mint</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Bull run</t>
+          <t>Double mint</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>立即生效：对手移速 +15%；劝退获得 GST +50%</t>
+          <t>所有装置每次出手有 20% 概率立刻再来一次</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>Instant: rivals +15% speed; +50% GST per runner stopped</t>
+          <t>Every device has a 20% chance to act again instantly</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>Immédiat : rivaux +15 % de vitesse ; +50 % de GST par coureur arrêté</t>
+          <t>Chaque dispositif a 20 % de chances d’agir à nouveau</t>
         </is>
       </c>
       <c r="L31" s="7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>v1 = 对手速度倍率，v2 = GST 倍率</t>
+          <t>概率见全局 twinChance</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>twin</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
@@ -3107,32 +3107,32 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>双倍铸造</t>
+          <t>Gas Hero 连环毒气</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Double Mint</t>
+          <t>Gas Hero Chain Gas</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Double mint</t>
+          <t>Gaz en chaîne Gas Hero</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>所有装置每次出手有 20% 概率立刻再来一次</t>
+          <t>毒气范围 +50%、效果翻倍</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>Every device has a 20% chance to act again instantly</t>
+          <t>Gas area +50%, effect doubled</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>Chaque dispositif a 20 % de chances d’agir à nouveau</t>
+          <t>Zone de gaz +50 %, effet doublé</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
@@ -3143,14 +3143,14 @@
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>概率见全局 twinChance</t>
+          <t>需先有 Gas Hero 毒气</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>chain</t>
+          <t>overclock</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
@@ -3171,32 +3171,32 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Gas Hero 连环毒气</t>
+          <t>马拉松模式</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Gas Hero Chain Gas</t>
+          <t>Marathon Mode</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Gaz en chaîne Gas Hero</t>
+          <t>Mode marathon</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>毒气范围 +50%、效果翻倍</t>
+          <t>燃脂模式持续 10 秒，出手速度 ×2</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>Gas area +50%, effect doubled</t>
+          <t>Fat-burn mode lasts 10 s at ×2 speed</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>Zone de gaz +50 %, effet doublé</t>
+          <t>Le mode brûle-graisse dure 10 s à vitesse ×2</t>
         </is>
       </c>
       <c r="L33" s="7" t="n">
@@ -3207,76 +3207,12 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>需先有 Gas Hero 毒气</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>overclock</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>道具</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>马拉松模式</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>Marathon Mode</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Mode marathon</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>燃脂模式持续 10 秒，出手速度 ×2</t>
-        </is>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>Fat-burn mode lasts 10 s at ×2 speed</t>
-        </is>
-      </c>
-      <c r="K34" s="8" t="inlineStr">
-        <is>
-          <t>Le mode brûle-graisse dure 10 s à vitesse ×2</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="9" t="inlineStr">
-        <is>
           <t>数值见全局</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>※ 徽章卡（m_ 开头）的名称和说明由装置简称自动生成，填写无效。稀有度权重在「全局」rarityC/R/L。</t>
         </is>
@@ -11166,7 +11102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:D304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -15006,2711 +14942,2821 @@
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>点跑道旁的石台放置装置，再点装置直接升级。</t>
+          <t>开跑！</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>点跑道旁的石台放置装置，再点装置直接升级。</t>
+          <t>开跑！</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Tap a stone pad beside the track to place a device, then tap the device to upgrade it.</t>
+          <t>Go!</t>
         </is>
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>Touchez un socle près de la piste pour poser un dispositif, puis touchez-le pour l’améliorer.</t>
+          <t>Partez !</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>开跑！</t>
+          <t>神秘箱开启中…</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>开跑！</t>
+          <t>神秘箱开启中…</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Go!</t>
+          <t>Opening the Mystery Box…</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Partez !</t>
+          <t>Ouverture de la Mystery Box…</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>神秘箱开启中…</t>
+          <t>准备…</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>神秘箱开启中…</t>
+          <t>准备…</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Opening the Mystery Box…</t>
+          <t>Get ready…</t>
         </is>
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>Ouverture de la Mystery Box…</t>
+          <t>Prêt…</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>准备…</t>
+          <t>建造装置</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>准备…</t>
+          <t>建造装置</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Get ready…</t>
+          <t>Build a device</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Prêt…</t>
+          <t>Construire</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>建造装置</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>建造装置</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Build a device</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>Construire</t>
+          <t>Fermer</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>已锁定</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>已锁定</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Fermer</t>
+          <t>Verrouillé</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>已锁定</t>
+          <t>主</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>已锁定</t>
+          <t>主</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>Verrouillé</t>
+          <t>Princ.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>主</t>
+          <t>次</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>主</t>
+          <t>次</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Princ.</t>
+          <t>Sec.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>次</t>
+          <t>回收 +{n}</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>次</t>
+          <t>回收 +{n}</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Recycle +{n}</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>Sec.</t>
+          <t>Recycler +{n}</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>回收 +{n}</t>
+          <t>跑步加成</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>回收 +{n}</t>
+          <t>跑步加成</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Recycle +{n}</t>
+          <t>Running boost</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Recycler +{n}</t>
+          <t>Bonus de course</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>跑步加成</t>
+          <t>真实跑步会让你的装置更强。原型里用下面的开关模拟；正式版自动读取你在 STEPN 的跑步数据。</t>
         </is>
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>跑步加成</t>
+          <t>真实跑步会让你的装置更强。原型里用下面的开关模拟；正式版自动读取你在 STEPN 的跑步数据。</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Running boost</t>
+          <t>Real runs make your devices stronger. In this prototype you simulate it with the controls below; the live version reads your STEPN running data automatically.</t>
         </is>
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Bonus de course</t>
+          <t>Courir pour de vrai renforce tes dispositifs. Dans ce prototype, simule-le ci-dessous ; la version finale lira automatiquement tes données de course STEPN.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>真实跑步会让你的装置更强。原型里用下面的开关模拟；正式版自动读取你在 STEPN 的跑步数据。</t>
+          <t>公会天赋（模拟累计 RP）</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>真实跑步会让你的装置更强。原型里用下面的开关模拟；正式版自动读取你在 STEPN 的跑步数据。</t>
+          <t>公会天赋（模拟累计 RP）</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Real runs make your devices stronger. In this prototype you simulate it with the controls below; the live version reads your STEPN running data automatically.</t>
+          <t>Guild talent (simulated total RP)</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Courir pour de vrai renforce tes dispositifs. Dans ce prototype, simule-le ci-dessous ; la version finale lira automatiquement tes données de course STEPN.</t>
+          <t>Talent de guilde (RP cumulés simulés)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>公会天赋（模拟累计 RP）</t>
+          <t>累计 {r} RP · 未解锁</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>公会天赋（模拟累计 RP）</t>
+          <t>累计 {r} RP · 未解锁</t>
         </is>
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Guild talent (simulated total RP)</t>
+          <t>{r} RP total · locked</t>
         </is>
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Talent de guilde (RP cumulés simulés)</t>
+          <t>{r} RP cumulés · verrouillé</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>累计 {r} RP · 未解锁</t>
+          <t>累计 {r} RP · {t} 档 +{b}%</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>累计 {r} RP · 未解锁</t>
+          <t>累计 {r} RP · {t} 档 +{b}%</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>{r} RP total · locked</t>
+          <t>{r} RP total · tier {t} +{b}%</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>{r} RP cumulés · verrouillé</t>
+          <t>{r} RP cumulés · palier {t} +{b} %</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>累计 {r} RP · {t} 档 +{b}%</t>
+          <t>今日热身：今天在 STEPN 已跑满 {k} km → 当天所有对局装置效果 +{b}%</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>累计 {r} RP · {t} 档 +{b}%</t>
+          <t>今日热身：今天在 STEPN 已跑满 {k} km → 当天所有对局装置效果 +{b}%</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>{r} RP total · tier {t} +{b}%</t>
+          <t>Warm-up: ran at least {k} km in STEPN today → all devices +{b}% effect in every run today</t>
         </is>
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>{r} RP cumulés · palier {t} +{b} %</t>
+          <t>Échauffement : au moins {k} km courus dans STEPN aujourd’hui → tous les dispositifs +{b} % d’effet dans chaque partie du jour</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>今日热身：今天在 STEPN 已跑满 {k} km → 当天所有对局装置效果 +{b}%</t>
+          <t>天赋怎么提高：每次真实跑步获得 RP（跑步积分）——前 5 km 每 km {a} RP，5–10 km 每 km {b} RP，单日最多 {c} RP。累计 RP 达到 {t1} / {t2} / {t3} 自动解锁一 / 二 / 三档公会天赋，全部装置效果 +{p1}% / +{p2}% / +{p3}%。按每周跑 4 次、每次 4.5 km 计算，大约 1 周、3 周、7 周解锁。</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>今日热身：今天在 STEPN 已跑满 {k} km → 当天所有对局装置效果 +{b}%</t>
+          <t>天赋怎么提高：每次真实跑步获得 RP（跑步积分）——前 5 km 每 km {a} RP，5–10 km 每 km {b} RP，单日最多 {c} RP。累计 RP 达到 {t1} / {t2} / {t3} 自动解锁一 / 二 / 三档公会天赋，全部装置效果 +{p1}% / +{p2}% / +{p3}%。按每周跑 4 次、每次 4.5 km 计算，大约 1 周、3 周、7 周解锁。</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Warm-up: ran at least {k} km in STEPN today → all devices +{b}% effect in every run today</t>
+          <t>How to raise your talent: every real run earns RP (Run Points) — {a} RP per km for the first 5 km, {b} RP per km from 5 to 10 km, up to {c} RP a day. Reaching {t1} / {t2} / {t3} total RP unlocks guild talent tier 1 / 2 / 3: all devices +{p1}% / +{p2}% / +{p3}% effect. Running 4 times a week at 4.5 km each, that takes about 1, 3 and 7 weeks.</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Échauffement : au moins {k} km courus dans STEPN aujourd’hui → tous les dispositifs +{b} % d’effet dans chaque partie du jour</t>
+          <t>Comment monter ton talent : chaque vraie course rapporte des RP (points de course) — {a} RP par km sur les 5 premiers km, {b} RP par km de 5 à 10 km, {c} RP max par jour. À {t1} / {t2} / {t3} RP cumulés, tu débloques le palier 1 / 2 / 3 du talent de guilde : tous les dispositifs +{p1} % / +{p2} % / +{p3} % d’effet. En courant 4 fois par semaine 4,5 km, comptez environ 1, 3 et 7 semaines.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>天赋怎么提高：每次真实跑步获得 RP（跑步积分）——前 5 km 每 km {a} RP，5–10 km 每 km {b} RP，单日最多 {c} RP。累计 RP 达到 {t1} / {t2} / {t3} 自动解锁一 / 二 / 三档公会天赋，全部装置效果 +{p1}% / +{p2}% / +{p3}%。按每周跑 4 次、每次 4.5 km 计算，大约 1 周、3 周、7 周解锁。</t>
+          <t>当前跑步加成：装置效果 +{n}%</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>天赋怎么提高：每次真实跑步获得 RP（跑步积分）——前 5 km 每 km {a} RP，5–10 km 每 km {b} RP，单日最多 {c} RP。累计 RP 达到 {t1} / {t2} / {t3} 自动解锁一 / 二 / 三档公会天赋，全部装置效果 +{p1}% / +{p2}% / +{p3}%。按每周跑 4 次、每次 4.5 km 计算，大约 1 周、3 周、7 周解锁。</t>
+          <t>当前跑步加成：装置效果 +{n}%</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>How to raise your talent: every real run earns RP (Run Points) — {a} RP per km for the first 5 km, {b} RP per km from 5 to 10 km, up to {c} RP a day. Reaching {t1} / {t2} / {t3} total RP unlocks guild talent tier 1 / 2 / 3: all devices +{p1}% / +{p2}% / +{p3}% effect. Running 4 times a week at 4.5 km each, that takes about 1, 3 and 7 weeks.</t>
+          <t>Current running boost: devices +{n}%</t>
         </is>
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Comment monter ton talent : chaque vraie course rapporte des RP (points de course) — {a} RP par km sur les 5 premiers km, {b} RP par km de 5 à 10 km, {c} RP max par jour. À {t1} / {t2} / {t3} RP cumulés, tu débloques le palier 1 / 2 / 3 du talent de guilde : tous les dispositifs +{p1} % / +{p2} % / +{p3} % d’effet. En courant 4 fois par semaine 4,5 km, comptez environ 1, 3 et 7 semaines.</t>
+          <t>Bonus de course actuel : dispositifs +{n} %</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>当前跑步加成：装置效果 +{n}%</t>
+          <t>跑步加成 +{n}%</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>当前跑步加成：装置效果 +{n}%</t>
+          <t>跑步加成 +{n}%</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Current running boost: devices +{n}%</t>
+          <t>Running boost +{n}%</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Bonus de course actuel : dispositifs +{n} %</t>
+          <t>Bonus de course +{n} %</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>跑步加成 +{n}%</t>
+          <t>宝石发射器</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>跑步加成 +{n}%</t>
+          <t>宝石发射器</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Running boost +{n}%</t>
+          <t>Gem Launcher</t>
         </is>
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Bonus de course +{n} %</t>
+          <t>Lance-gemmes</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>点跑道旁的石台放置装置，再点「开始第 1 波」</t>
+          <t>红宝石</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>点跑道旁的石台放置装置，再点「开始第 1 波」</t>
+          <t>红宝石</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Tap a stone pad beside the track to place a device, then press “Start wave 1”</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Touchez un socle près de la piste pour poser un dispositif, puis « Lancer la vague 1 »</t>
+          <t>Rubis</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>宝石发射器</t>
+          <t>蓝宝石</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>宝石发射器</t>
+          <t>蓝宝石</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Gem Launcher</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Lance-gemmes</t>
+          <t>Saphir</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>红宝石</t>
+          <t>下一级：{x}</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>红宝石</t>
+          <t>下一级：{x}</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Next: {x}</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Rubis</t>
+          <t>Suivant : {x}</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>蓝宝石</t>
+          <t>这里不能放</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>蓝宝石</t>
+          <t>这里不能放</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>Can’t build here</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Saphir</t>
+          <t>Impossible ici</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>下一级：{x}</t>
+          <t>取消放置</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>下一级：{x}</t>
+          <t>取消放置</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Next: {x}</t>
+          <t>Cancel placing</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Suivant : {x}</t>
+          <t>Annuler</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>这里不能放</t>
+          <t>＋ 放置点 ×{n}</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>这里不能放</t>
+          <t>＋ 放置点 ×{n}</t>
         </is>
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Can’t place here</t>
+          <t>+ Spot ×{n}</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Impossible ici</t>
+          <t>+ Emplacement ×{n}</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>取消放置</t>
+          <t>点跑道外的空地，新增一个放置点</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>取消放置</t>
+          <t>点跑道外的空地，新增一个放置点</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Cancel placing</t>
+          <t>Tap open ground off the track to add a spot</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Touche un terrain libre hors piste pour ajouter un emplacement</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>＋ 放置点 ×{n}</t>
+          <t>聪</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>＋ 放置点 ×{n}</t>
+          <t>聪</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>+ Spot ×{n}</t>
+          <t>sats</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>+ Emplacement ×{n}</t>
+          <t>sats</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>点跑道外的空地，新增一个放置点</t>
+          <t>创世纪 · 2008–2010</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>点跑道外的空地，新增一个放置点</t>
+          <t>创世纪 · 2008–2010</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Tap open ground off the track to add a spot</t>
+          <t>Genesis · 2008–2010</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Touche un terrain libre hors piste pour ajouter un emplacement</t>
+          <t>Genèse · 2008–2010</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>聪</t>
+          <t>组合</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>聪</t>
+          <t>组合</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>sats</t>
+          <t>Combos</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>sats</t>
+          <t>Combos</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>创世纪 · 2008–2010</t>
+          <t>重试</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>创世纪 · 2008–2010</t>
+          <t>重试</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Genesis · 2008–2010</t>
+          <t>Retry</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Genèse · 2008–2010</t>
+          <t>Réessayer</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>组合</t>
+          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>组合</t>
+          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
         <is>
-          <t>Combos</t>
+          <t>A STEPN runner falls into a blockchain time tunnel and lives through bitcoin’s first three years.</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>Combos</t>
+          <t>Un coureur STEPN tombe dans un tunnel temporel blockchain et vit les trois premières années du bitcoin.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>重试</t>
+          <t>累计积分 {n}</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>重试</t>
+          <t>累计积分 {n}</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Retry</t>
+          <t>Points: {n}</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Réessayer</t>
+          <t>Points : {n}</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
+          <t>剧情中…</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
+          <t>剧情中…</t>
         </is>
       </c>
       <c r="C207" s="8" t="inlineStr">
         <is>
-          <t>A STEPN runner falls into a blockchain time tunnel and lives through bitcoin’s first three years.</t>
+          <t>Story…</t>
         </is>
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>Un coureur STEPN tombe dans un tunnel temporel blockchain et vit les trois premières années du bitcoin.</t>
+          <t>Histoire…</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>累计积分 {n}</t>
+          <t>关卡完成</t>
         </is>
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>累计积分 {n}</t>
+          <t>关卡完成</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Points: {n}</t>
+          <t>Level complete</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Points : {n}</t>
+          <t>Niveau terminé</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>剧情中…</t>
+          <t>再玩一次</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>剧情中…</t>
+          <t>再玩一次</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>Story…</t>
+          <t>Play again</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Histoire…</t>
+          <t>Rejouer</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>关卡完成</t>
+          <t>章节地图</t>
         </is>
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>关卡完成</t>
+          <t>章节地图</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Level complete</t>
+          <t>Chapter map</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Niveau terminé</t>
+          <t>Carte du chapitre</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>再玩一次</t>
+          <t>第二章 · 敬请期待</t>
         </is>
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>再玩一次</t>
+          <t>第二章 · 敬请期待</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>Play again</t>
+          <t>Chapter 2 · coming soon</t>
         </is>
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Rejouer</t>
+          <t>Chapitre 2 · bientôt</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>章节地图</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>章节地图</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Chapter map</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Carte du chapitre</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>第二章 · 敬请期待</t>
+          <t>区块高度</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>第二章 · 敬请期待</t>
+          <t>区块高度</t>
         </is>
       </c>
       <c r="C213" s="8" t="inlineStr">
         <is>
-          <t>Chapter 2 · coming soon</t>
+          <t>Block height</t>
         </is>
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>Chapitre 2 · bientôt</t>
+          <t>Hauteur</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>区块奖励：选一个，比赛马上继续。</t>
         </is>
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>区块奖励：选一个，比赛马上继续。</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Block reward: pick one and the race resumes.</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Récompense de bloc : choisis-en une et la course reprend.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>区块高度</t>
+          <t>选择关卡</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>区块高度</t>
+          <t>选择关卡</t>
         </is>
       </c>
       <c r="C215" s="8" t="inlineStr">
         <is>
-          <t>Block height</t>
+          <t>Choose a level</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Hauteur</t>
+          <t>Choisir un niveau</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>区块奖励：选一个，比赛马上继续。</t>
+          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>区块奖励：选一个，比赛马上继续。</t>
+          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Block reward: pick one and the race resumes.</t>
+          <t>No combos this time. Try stacking two statuses on the same runner.</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Récompense de bloc : choisis-en une et la course reprend.</t>
+          <t>Aucun combo cette fois. Essaie de cumuler deux états sur le même coureur.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>选择关卡</t>
+          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>选择关卡</t>
+          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
         </is>
       </c>
       <c r="C217" s="8" t="inlineStr">
         <is>
-          <t>Choose a level</t>
+          <t>Keys: Space start wave · F speed · 1–7 build · Q/W/E upgrade · X recycle · Esc cancel</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Choisir un niveau</t>
+          <t>Touches : Espace vague · F vitesse · 1–7 construire · Q/W/E améliorer · X recycler · Échap annuler</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
+          <t>一万枚换两个披萨！</t>
         </is>
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
+          <t>一万枚换两个披萨！</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>No combos this time. Try stacking two statuses on the same runner.</t>
+          <t>10,000 coins for two pizzas!</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Aucun combo cette fois. Essaie de cumuler deux états sur le même coureur.</t>
+          <t>10 000 pièces pour deux pizzas !</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
+          <t>知识卡</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
+          <t>知识卡</t>
         </is>
       </c>
       <c r="C219" s="8" t="inlineStr">
         <is>
-          <t>Keys: Space start wave · F speed · 1–7 build · Q/W/E upgrade · X recycle · Esc cancel</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Touches : Espace vague · F vitesse · 1–7 construire · Q/W/E améliorer · X recycler · Échap annuler</t>
+          <t>Savoir</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>一万枚换两个披萨！</t>
+          <t>新组合：{x}！</t>
         </is>
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>一万枚换两个披萨！</t>
+          <t>新组合：{x}！</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>10,000 coins for two pizzas!</t>
+          <t>New combo: {x}!</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>10 000 pièces pour deux pizzas !</t>
+          <t>Nouveau combo : {x} !</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>知识卡</t>
+          <t>下一关</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>知识卡</t>
+          <t>下一关</t>
         </is>
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>Knowledge</t>
+          <t>Next level</t>
         </is>
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Savoir</t>
+          <t>Niveau suivant</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>新组合：{x}！</t>
+          <t>{n}× 速度</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>新组合：{x}！</t>
+          <t>{n}× 速度</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>New combo: {x}!</t>
+          <t>{n}× speed</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Nouveau combo : {x} !</t>
+          <t>Vitesse ×{n}</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>下一关</t>
+          <t>区块 #{h} 被别的矿工抢先挖到了</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>下一关</t>
+          <t>区块 #{h} 被别的矿工抢先挖到了</t>
         </is>
       </c>
       <c r="C223" s="8" t="inlineStr">
         <is>
-          <t>Next level</t>
+          <t>Block #{h} went to another miner</t>
         </is>
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Niveau suivant</t>
+          <t>Le bloc #{h} est allé à un autre mineur</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>{n}× 速度</t>
+          <t>挖到区块</t>
         </is>
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>{n}× 速度</t>
+          <t>挖到区块</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>{n}× speed</t>
+          <t>Blocks mined</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Vitesse ×{n}</t>
+          <t>Blocs minés</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>区块 #{h} 被别的矿工抢先挖到了</t>
+          <t>本关触发的组合</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>区块 #{h} 被别的矿工抢先挖到了</t>
+          <t>本关触发的组合</t>
         </is>
       </c>
       <c r="C225" s="8" t="inlineStr">
         <is>
-          <t>Block #{h} went to another miner</t>
+          <t>Combos this level</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Le bloc #{h} est allé à un autre mineur</t>
+          <t>Combos de ce niveau</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>挖到区块</t>
+          <t>组合：{x}</t>
         </is>
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>挖到区块</t>
+          <t>组合：{x}</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Blocks mined</t>
+          <t>Combos: {x}</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Blocs minés</t>
+          <t>Combos : {x}</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>本关触发的组合</t>
+          <t>修复版本上线，溢出的币被回滚</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>本关触发的组合</t>
+          <t>修复版本上线，溢出的币被回滚</t>
         </is>
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>Combos this level</t>
+          <t>The fix is live; the overflowed coins are rolled back</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Combos de ce niveau</t>
+          <t>Le correctif est en ligne ; les pièces en trop sont annulées</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>组合：{x}</t>
+          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>组合：{x}</t>
+          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Combos: {x}</t>
+          <t>Not triggered yet. Try stacking these two statuses on one runner.</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Combos : {x}</t>
+          <t>Pas encore déclenché. Cumule ces deux états sur un coureur.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>修复版本上线，溢出的币被回滚</t>
+          <t>出块！#{h}</t>
         </is>
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>修复版本上线，溢出的币被回滚</t>
+          <t>出块！#{h}</t>
         </is>
       </c>
       <c r="C229" s="8" t="inlineStr">
         <is>
-          <t>The fix is live; the overflowed coins are rolled back</t>
+          <t>Block! #{h}</t>
         </is>
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>Le correctif est en ligne ; les pièces en trop sont annulées</t>
+          <t>Bloc ! #{h}</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
+          <t>挖到区块 #{h}！</t>
         </is>
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
+          <t>挖到区块 #{h}！</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Not triggered yet. Try stacking these two statuses on one runner.</t>
+          <t>Mined block #{h}!</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Pas encore déclenché. Cumule ces deux états sur un coureur.</t>
+          <t>Bloc #{h} miné !</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>出块！#{h}</t>
+          <t>披萨跑者冲出来了</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>出块！#{h}</t>
+          <t>披萨跑者冲出来了</t>
         </is>
       </c>
       <c r="C231" s="8" t="inlineStr">
         <is>
-          <t>Block! #{h}</t>
+          <t>Pizza runners incoming</t>
         </is>
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>Bloc ! #{h}</t>
+          <t>Les coureurs-pizza arrivent</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>挖到区块 #{h}！</t>
+          <t>重抽 · {n} 聪</t>
         </is>
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>挖到区块 #{h}！</t>
+          <t>重抽 · {n} 聪</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Mined block #{h}!</t>
+          <t>Reroll · {n} sats</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Bloc #{h} miné !</t>
+          <t>Relancer · {n} sats</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>披萨跑者冲出来了</t>
+          <t>继续 ▶</t>
         </is>
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>披萨跑者冲出来了</t>
+          <t>继续 ▶</t>
         </is>
       </c>
       <c r="C233" s="8" t="inlineStr">
         <is>
-          <t>Pizza runners incoming</t>
+          <t>Next ▶</t>
         </is>
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Les coureurs-pizza arrivent</t>
+          <t>Suite ▶</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>重抽 · {n} 聪</t>
+          <t>收入图鉴</t>
         </is>
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>重抽 · {n} 聪</t>
+          <t>收入图鉴</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Reroll · {n} sats</t>
+          <t>Add to codex</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Relancer · {n} sats</t>
+          <t>Ajouter au codex</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>继续 ▶</t>
+          <t>返回章节地图</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>继续 ▶</t>
+          <t>返回章节地图</t>
         </is>
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
-          <t>Next ▶</t>
+          <t>Back to chapter map</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Suite ▶</t>
+          <t>Retour à la carte</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>收入图鉴</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>收入图鉴</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Add to codex</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Ajouter au codex</t>
+          <t>Passer</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>返回章节地图</t>
+          <t>经典模式</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>返回章节地图</t>
+          <t>经典模式</t>
         </is>
       </c>
       <c r="C237" s="8" t="inlineStr">
         <is>
-          <t>Back to chapter map</t>
+          <t>Classic mode</t>
         </is>
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>Retour à la carte</t>
+          <t>Mode classique</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>开始！</t>
         </is>
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>开始！</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Go!</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>Passer</t>
+          <t>C’est parti !</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>经典模式</t>
+          <t>算力 {h} · 出块奖励 +{b}%</t>
         </is>
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>经典模式</t>
+          <t>算力 {h} · 出块奖励 +{b}%</t>
         </is>
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
-          <t>Classic mode</t>
+          <t>Hash {h} · block reward +{b}%</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>Mode classique</t>
+          <t>Puissance {h} · récompense +{b} %</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>开始！</t>
+          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
         </is>
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>开始！</t>
+          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Go!</t>
+          <t>The network makes a block every dozen seconds or so. Your share of total hash power is your chance of winning it. Win a block: sats plus a pick-one-of-three.</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>C’est parti !</t>
+          <t>Le réseau produit un bloc toutes les quinze secondes environ. Ta part de la puissance totale est ta chance de le gagner. Bloc gagné : des sats et un choix parmi trois.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>算力 {h} · 出块奖励 +{b}%</t>
+          <t>出块几率</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>算力 {h} · 出块奖励 +{b}%</t>
+          <t>出块几率</t>
         </is>
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>Hash {h} · block reward +{b}%</t>
+          <t>Win chance</t>
         </is>
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>Puissance {h} · récompense +{b} %</t>
+          <t>Chance</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
+          <t>软分叉！</t>
         </is>
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
+          <t>软分叉！</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>The network makes a block every dozen seconds or so. Your share of total hash power is your chance of winning it. Win a block: sats plus a pick-one-of-three.</t>
+          <t>Soft fork!</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>Le réseau produit un bloc toutes les quinze secondes environ. Ta part de la puissance totale est ta chance de le gagner. Bloc gagné : des sats et un choix parmi trois.</t>
+          <t>Soft fork !</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>出块几率</t>
+          <t>原型阶段的链下积分，没有任何实际价值</t>
         </is>
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>出块几率</t>
+          <t>原型阶段的链下积分，没有任何实际价值</t>
         </is>
       </c>
       <c r="C243" s="8" t="inlineStr">
         <is>
-          <t>Win chance</t>
+          <t>off-chain prototype points with no real-world value</t>
         </is>
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>Chance</t>
+          <t>points hors chaîne du prototype, sans valeur réelle</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>软分叉！</t>
+          <t>你的算力</t>
         </is>
       </c>
       <c r="B244" s="8" t="inlineStr">
         <is>
-          <t>软分叉！</t>
+          <t>你的算力</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Soft fork!</t>
+          <t>Your hash</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Soft fork !</t>
+          <t>Ta puissance</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>原型阶段的链下积分，没有任何实际价值</t>
+          <t>挖到的聪</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>原型阶段的链下积分，没有任何实际价值</t>
+          <t>挖到的聪</t>
         </is>
       </c>
       <c r="C245" s="8" t="inlineStr">
         <is>
-          <t>off-chain prototype points with no real-world value</t>
+          <t>Sats mined</t>
         </is>
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>points hors chaîne du prototype, sans valeur réelle</t>
+          <t>Sats minés</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>你的算力</t>
+          <t>全网算力</t>
         </is>
       </c>
       <c r="B246" s="8" t="inlineStr">
         <is>
-          <t>你的算力</t>
+          <t>全网算力</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>Your hash</t>
+          <t>Network hash</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Ta puissance</t>
+          <t>Puissance réseau</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>挖到的聪</t>
+          <t>已挖到</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>挖到的聪</t>
+          <t>已挖到</t>
         </is>
       </c>
       <c r="C247" s="8" t="inlineStr">
         <is>
-          <t>Sats mined</t>
+          <t>Won</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>Sats minés</t>
+          <t>Gagnés</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>全网算力</t>
+          <t>下个区块</t>
         </is>
       </c>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t>全网算力</t>
+          <t>下个区块</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>Network hash</t>
+          <t>Next block</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Puissance réseau</t>
+          <t>Prochain bloc</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>已挖到</t>
+          <t>剩余生命</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>已挖到</t>
+          <t>剩余生命</t>
         </is>
       </c>
       <c r="C249" s="8" t="inlineStr">
         <is>
-          <t>Won</t>
+          <t>Lives left</t>
         </is>
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>Gagnés</t>
+          <t>Vies restantes</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>下个区块</t>
+          <t>快捷键 Q / W / E 升级，X 回收</t>
         </is>
       </c>
       <c r="B250" s="8" t="inlineStr">
         <is>
-          <t>下个区块</t>
+          <t>快捷键 Q / W / E 升级，X 回收</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Next block</t>
+          <t>Keys Q / W / E upgrade, X recycles</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Prochain bloc</t>
+          <t>Touches Q / W / E améliorer, X recycler</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>剩余生命</t>
+          <t>整数溢出！</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>剩余生命</t>
+          <t>整数溢出！</t>
         </is>
       </c>
       <c r="C251" s="8" t="inlineStr">
         <is>
-          <t>Lives left</t>
+          <t>Integer overflow!</t>
         </is>
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>Vies restantes</t>
+          <t>Dépassement d’entier !</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>快捷键 Q / W / E 升级，X 回收</t>
+          <t>第一章</t>
         </is>
       </c>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>快捷键 Q / W / E 升级，X 回收</t>
+          <t>第一章</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Keys Q / W / E upgrade, X recycles</t>
+          <t>Chapter 1</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Touches Q / W / E améliorer, X recycler</t>
+          <t>Chapitre 1</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>整数溢出！</t>
+          <t>通关「{x}」解锁</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>整数溢出！</t>
+          <t>通关「{x}」解锁</t>
         </is>
       </c>
       <c r="C253" s="8" t="inlineStr">
         <is>
-          <t>Integer overflow!</t>
+          <t>Clear “{x}” to unlock</t>
         </is>
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>Dépassement d’entier !</t>
+          <t>Termine « {x} » pour débloquer</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>第一章</t>
+          <t>挂上：{x}</t>
         </is>
       </c>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>第一章</t>
+          <t>挂上：{x}</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Chapter 1</t>
+          <t>Applies: {x}</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Chapitre 1</t>
+          <t>Applique : {x}</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>通关「{x}」解锁</t>
+          <t>难度调整：全网算力 +{n}%</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>通关「{x}」解锁</t>
+          <t>难度调整：全网算力 +{n}%</t>
         </is>
       </c>
       <c r="C255" s="8" t="inlineStr">
         <is>
-          <t>Clear “{x}” to unlock</t>
+          <t>Difficulty adjustment: network hash +{n}%</t>
         </is>
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>Termine « {x} » pour débloquer</t>
+          <t>Ajustement de difficulté : puissance réseau +{n} %</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>挂上：{x}</t>
+          <t>新知识卡</t>
         </is>
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t>挂上：{x}</t>
+          <t>新知识卡</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Applies: {x}</t>
+          <t>New knowledge card</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>Applique : {x}</t>
+          <t>Nouvelle carte savoir</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>难度调整：全网算力 +{n}%</t>
+          <t>⛏ 挖矿</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>难度调整：全网算力 +{n}%</t>
+          <t>⛏ 挖矿</t>
         </is>
       </c>
       <c r="C257" s="8" t="inlineStr">
         <is>
-          <t>Difficulty adjustment: network hash +{n}%</t>
+          <t>⛏ Mining</t>
         </is>
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>Ajustement de difficulté : puissance réseau +{n} %</t>
+          <t>⛏ Minage</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>新知识卡</t>
+          <t>获得积分</t>
         </is>
       </c>
       <c r="B258" s="8" t="inlineStr">
         <is>
-          <t>新知识卡</t>
+          <t>获得积分</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>New knowledge card</t>
+          <t>Points earned</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>Nouvelle carte savoir</t>
+          <t>Points gagnés</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>⛏ 挖矿</t>
+          <t>再点一次离开（本局进度不保存）</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>⛏ 挖矿</t>
+          <t>再点一次离开（本局进度不保存）</t>
         </is>
       </c>
       <c r="C259" s="8" t="inlineStr">
         <is>
-          <t>⛏ Mining</t>
+          <t>Tap again to leave (this run is not saved)</t>
         </is>
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>⛏ Minage</t>
+          <t>Touche encore pour quitter (partie non sauvegardée)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>获得积分</t>
+          <t>皮厚</t>
         </is>
       </c>
       <c r="B260" s="8" t="inlineStr">
         <is>
-          <t>获得积分</t>
+          <t>皮厚</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Points earned</t>
+          <t>Tough</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>Points gagnés</t>
+          <t>Coriace</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>再点一次离开（本局进度不保存）</t>
+          <t>防水</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>再点一次离开（本局进度不保存）</t>
+          <t>防水</t>
         </is>
       </c>
       <c r="C261" s="8" t="inlineStr">
         <is>
-          <t>Tap again to leave (this run is not saved)</t>
+          <t>Waterproof</t>
         </is>
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Touche encore pour quitter (partie non sauvegardée)</t>
+          <t>Imperméable</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>皮厚</t>
+          <t>跳过！</t>
         </is>
       </c>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t>皮厚</t>
+          <t>跳过！</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Tough</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Coriace</t>
+          <t>Hop !</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>防水</t>
+          <t>跑者</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>防水</t>
+          <t>跑者</t>
         </is>
       </c>
       <c r="C263" s="8" t="inlineStr">
         <is>
-          <t>Waterproof</t>
+          <t>Runners</t>
         </is>
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Imperméable</t>
+          <t>Coureurs</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>跳过！</t>
+          <t>对策</t>
         </is>
       </c>
       <c r="B264" s="8" t="inlineStr">
         <is>
-          <t>跳过！</t>
+          <t>对策</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Counter</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Hop !</t>
+          <t>Parade</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>跑者</t>
+          <t>还没遇到过。</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>跑者</t>
+          <t>还没遇到过。</t>
         </is>
       </c>
       <c r="C265" s="8" t="inlineStr">
         <is>
-          <t>Runners</t>
+          <t>Not met yet.</t>
         </is>
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Coureurs</t>
+          <t>Pas encore croisé.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>对策</t>
+          <t>新跑者</t>
         </is>
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>对策</t>
+          <t>新跑者</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>Counter</t>
+          <t>New runner</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>Parade</t>
+          <t>Nouveau coureur</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>还没遇到过。</t>
+          <t>对{x}无效</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>还没遇到过。</t>
+          <t>对{x}无效</t>
         </is>
       </c>
       <c r="C267" s="8" t="inlineStr">
         <is>
-          <t>Not met yet.</t>
+          <t>No effect on {x}</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Pas encore croisé.</t>
+          <t>Sans effet sur {x}</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>新跑者</t>
+          <t>连撞 ×{n}</t>
         </is>
       </c>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t>新跑者</t>
+          <t>连撞 ×{n}</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>New runner</t>
+          <t>Crash ×{n}</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Nouveau coureur</t>
+          <t>Collision ×{n}</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>对{x}无效</t>
+          <t>整道铺皮！</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>对{x}无效</t>
+          <t>整道铺皮！</t>
         </is>
       </c>
       <c r="C269" s="8" t="inlineStr">
         <is>
-          <t>No effect on {x}</t>
+          <t>Paved with peels!</t>
         </is>
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Sans effet sur {x}</t>
+          <t>Piste couverte !</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>连撞 ×{n}</t>
+          <t>后勤补给！</t>
         </is>
       </c>
       <c r="B270" s="8" t="inlineStr">
         <is>
-          <t>连撞 ×{n}</t>
+          <t>后勤补给！</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>Crash ×{n}</t>
+          <t>Supplies in!</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Collision ×{n}</t>
+          <t>Ravitaillement !</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>整道铺皮！</t>
+          <t>重低音 ×{n}</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>整道铺皮！</t>
+          <t>重低音 ×{n}</t>
         </is>
       </c>
       <c r="C271" s="8" t="inlineStr">
         <is>
-          <t>Paved with peels!</t>
+          <t>Bass drop ×{n}</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Piste couverte !</t>
+          <t>Basse ×{n}</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>后勤补给！</t>
+          <t>限量发售！</t>
         </is>
       </c>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t>后勤补给！</t>
+          <t>限量发售！</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Supplies in!</t>
+          <t>Launch event!</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Ravitaillement !</t>
+          <t>Lancement !</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>重低音 ×{n}</t>
+          <t>投递区已设定</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>重低音 ×{n}</t>
+          <t>投递区已设定</t>
         </is>
       </c>
       <c r="C273" s="8" t="inlineStr">
         <is>
-          <t>Bass drop ×{n}</t>
+          <t>Drop zone set</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Basse ×{n}</t>
+          <t>Zone de largage fixée</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>限量发售！</t>
+          <t>布阵路段已设定</t>
         </is>
       </c>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>限量发售！</t>
+          <t>布阵路段已设定</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Launch event!</t>
+          <t>Trap stretch set</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Lancement !</t>
+          <t>Tronçon piégé fixé</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>投递区已设定</t>
+          <t>副路线最多 2 级</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>投递区已设定</t>
+          <t>副路线最多 2 级</t>
         </is>
       </c>
       <c r="C275" s="8" t="inlineStr">
         <is>
-          <t>Drop zone set</t>
+          <t>Secondary path max tier 2</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Zone de largage fixée</t>
+          <t>Voie secondaire : niveau 2 max</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>布阵路段已设定</t>
+          <t>6 级专精 −30%</t>
         </is>
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>布阵路段已设定</t>
+          <t>6 级专精 −30%</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Trap stretch set</t>
+          <t>Tier-6 specialisation −30%</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Tronçon piégé fixé</t>
+          <t>Spécialisation niv. 6 −30 %</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>副路线最多 2 级</t>
+          <t>副</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>副路线最多 2 级</t>
+          <t>副</t>
         </is>
       </c>
       <c r="C277" s="8" t="inlineStr">
         <is>
-          <t>Secondary path max tier 2</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Voie secondaire : niveau 2 max</t>
+          <t>2e</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>6 级专精 −30%</t>
+          <t>副路线</t>
         </is>
       </c>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t>6 级专精 −30%</t>
+          <t>副路线</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Tier-6 specialisation −30%</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Spécialisation niv. 6 −30 %</t>
+          <t>Secondaire</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>副</t>
+          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>副</t>
+          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
         </is>
       </c>
       <c r="C279" s="8" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Tier 6 removes the secondary path; the {n} GST spent on it is credited</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>Le niveau 6 retire la voie secondaire ; les {n} GST dépensés sont déduits</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>副路线</t>
+          <t>点地图上的跑道…</t>
         </is>
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>副路线</t>
+          <t>点地图上的跑道…</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Tap the track…</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Secondaire</t>
+          <t>Touche la piste…</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
+          <t>🎯 设定投递区</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
+          <t>🎯 设定投递区</t>
         </is>
       </c>
       <c r="C281" s="8" t="inlineStr">
         <is>
-          <t>Tier 6 removes the secondary path; the {n} GST spent on it is credited</t>
+          <t>🎯 Set drop zone</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Le niveau 6 retire la voie secondaire ; les {n} GST dépensés sont déduits</t>
+          <t>🎯 Zone de largage</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>点地图上的跑道…</t>
+          <t>🎯 设定布阵路段</t>
         </is>
       </c>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t>点地图上的跑道…</t>
+          <t>🎯 设定布阵路段</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>Tap the track…</t>
+          <t>🎯 Set trap stretch</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste…</t>
+          <t>🎯 Tronçon à piéger</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>🎯 设定投递区</t>
+          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>🎯 设定投递区</t>
+          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
         </is>
       </c>
       <c r="C283" s="8" t="inlineStr">
         <is>
-          <t>🎯 Set drop zone</t>
+          <t>Two paths can each reach tier 2; the first to tier 3 becomes main (up to 5); tier 6 specialisation removes the secondary</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>🎯 Zone de largage</t>
+          <t>Deux voies peuvent atteindre le niveau 2 ; la première au niveau 3 devient principale (jusqu’à 5) ; la spécialisation niv. 6 retire la secondaire</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>🎯 设定布阵路段</t>
+          <t>{x} 专精！</t>
         </is>
       </c>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t>🎯 设定布阵路段</t>
+          <t>{x} 专精！</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>🎯 Set trap stretch</t>
+          <t>{x} specialisation!</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>🎯 Tronçon à piéger</t>
+          <t>Spécialisation : {x} !</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
+          <t>场上上限</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
+          <t>场上上限</t>
         </is>
       </c>
       <c r="C285" s="8" t="inlineStr">
         <is>
-          <t>Two paths can each reach tier 2; the first to tier 3 becomes main (up to 5); tier 6 specialisation removes the secondary</t>
+          <t>Max on track</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Deux voies peuvent atteindre le niveau 2 ; la première au niveau 3 devient principale (jusqu’à 5) ; la spécialisation niv. 6 retire la secondaire</t>
+          <t>Max sur piste</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>点跑道旁的石台放置装置，再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+          <t>每次箱数</t>
         </is>
       </c>
       <c r="B286" s="8" t="inlineStr">
         <is>
-          <t>点跑道旁的石台放置装置，再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+          <t>每次箱数</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>Tap a stone pad by the track to place a device, then tap it to upgrade. Each device can grow two paths: both can reach tier 2, the first to tier 3 becomes main and goes up to 5; tier 6 specialisation removes the secondary path and credits what you spent on it.</t>
+          <t>Boxes per run</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Touche un socle près de la piste pour poser un dispositif, puis touche-le pour l’améliorer. Deux voies maximum : les deux peuvent atteindre le niveau 2, la première au niveau 3 devient principale jusqu’au 5 ; la spécialisation niv. 6 retire la secondaire et déduit ce que tu y as dépensé.</t>
+          <t>Boîtes par sortie</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>{x} 专精！</t>
+          <t>每次招呼</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>{x} 专精！</t>
+          <t>每次招呼</t>
         </is>
       </c>
       <c r="C287" s="8" t="inlineStr">
         <is>
-          <t>{x} specialisation!</t>
+          <t>Per invite</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Spécialisation : {x} !</t>
+          <t>Par invitation</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>场上上限</t>
+          <t>停留</t>
         </is>
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>场上上限</t>
+          <t>停留</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>Max on track</t>
+          <t>Stay</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Max sur piste</t>
+          <t>Arrêt</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>每次箱数</t>
+          <t>{x} 的动画 JSON 读不出来</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>每次箱数</t>
+          <t>{x} 的动画 JSON 读不出来</t>
         </is>
       </c>
       <c r="C289" s="8" t="inlineStr">
         <is>
-          <t>Boxes per run</t>
+          <t>Could not read the animation JSON for {x}</t>
         </is>
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Boîtes par sortie</t>
+          <t>Impossible de lire le JSON d’animation de {x}</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>每次招呼</t>
+          <t>弹道 {x} {k}</t>
         </is>
       </c>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>每次招呼</t>
+          <t>弹道 {x} {k}</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Per invite</t>
+          <t>Trajectory {x} {k}</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Par invitation</t>
+          <t>Trajectoire {x} {k}</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>停留</t>
+          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>停留</t>
+          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
         </is>
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Device {x}: base extra effect “{y}” is malformed, kept the original</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Arrêt</t>
+          <t>Dispositif {x} : effet de base « {y} » mal écrit, original conservé</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>{x} 的动画 JSON 读不出来</t>
+          <t>导入美术图片 / 动画（可多选）</t>
         </is>
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>{x} 的动画 JSON 读不出来</t>
+          <t>导入美术图片 / 动画（可多选）</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Could not read the animation JSON for {x}</t>
+          <t>Import art / animations (multi-select)</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Impossible de lire le JSON d’animation de {x}</t>
+          <t>Importer images / animations (plusieurs)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>弹道 {x} {k}</t>
+          <t>点跑道，设定投递区（Esc 取消）</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>弹道 {x} {k}</t>
+          <t>点跑道，设定投递区（Esc 取消）</t>
         </is>
       </c>
       <c r="C293" s="8" t="inlineStr">
         <is>
-          <t>Trajectory {x} {k}</t>
+          <t>Tap the track to set the drop zone (Esc to cancel)</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Trajectoire {x} {k}</t>
+          <t>Touche la piste pour choisir la zone de largage (Échap pour annuler)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
+          <t>点跑道，设定布阵路段（Esc 取消）</t>
         </is>
       </c>
       <c r="B294" s="8" t="inlineStr">
         <is>
-          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
+          <t>点跑道，设定布阵路段（Esc 取消）</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Device {x}: base extra effect “{y}” is malformed, kept the original</t>
+          <t>Tap the track to set the trap stretch (Esc to cancel)</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Dispositif {x} : effet de base « {y} » mal écrit, original conservé</t>
+          <t>Touche la piste pour choisir le tronçon à piéger (Échap pour annuler)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>导入美术图片 / 动画（可多选）</t>
+          <t>放不下</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>导入美术图片 / 动画（可多选）</t>
+          <t>放不下</t>
         </is>
       </c>
       <c r="C295" s="8" t="inlineStr">
         <is>
-          <t>Import art / animations (multi-select)</t>
+          <t>No room</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Importer images / animations (plusieurs)</t>
+          <t>Pas de place</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>点跑道，设定投递区（Esc 取消）</t>
+          <t>再点一次重新开始</t>
         </is>
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>点跑道，设定投递区（Esc 取消）</t>
+          <t>再点一次重新开始</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Tap the track to set the drop zone (Esc to cancel)</t>
+          <t>Tap again to restart</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste pour choisir la zone de largage (Échap pour annuler)</t>
+          <t>Touche encore pour recommencer</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>点跑道，设定布阵路段（Esc 取消）</t>
+          <t>重开本关</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>点跑道，设定布阵路段（Esc 取消）</t>
+          <t>重开本关</t>
         </is>
       </c>
       <c r="C297" s="8" t="inlineStr">
         <is>
-          <t>Tap the track to set the trap stretch (Esc to cancel)</t>
+          <t>Restart level</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste pour choisir le tronçon à piéger (Échap pour annuler)</t>
+          <t>Rejouer le niveau</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>重新开始</t>
+        </is>
+      </c>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>重新开始</t>
+        </is>
+      </c>
+      <c r="C298" s="8" t="inlineStr">
+        <is>
+          <t>Restart</t>
+        </is>
+      </c>
+      <c r="D298" s="8" t="inlineStr">
+        <is>
+          <t>Recommencer</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="10" t="inlineStr">
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>↻ 重新开始</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
+        <is>
+          <t>↻ 重新开始</t>
+        </is>
+      </c>
+      <c r="C299" s="8" t="inlineStr">
+        <is>
+          <t>↻ Restart</t>
+        </is>
+      </c>
+      <c r="D299" s="8" t="inlineStr">
+        <is>
+          <t>↻ Recommencer</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+        </is>
+      </c>
+      <c r="B300" s="8" t="inlineStr">
+        <is>
+          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+        </is>
+      </c>
+      <c r="C300" s="8" t="inlineStr">
+        <is>
+          <t>Tap any free ground off the track to place a device (each device takes a different number of cells), then tap it to upgrade. Each device can grow two paths: both can reach tier 2, the first to tier 3 becomes main and goes up to 5; tier 6 specialisation removes the secondary path and credits what you spent on it.</t>
+        </is>
+      </c>
+      <c r="D300" s="8" t="inlineStr">
+        <is>
+          <t>Touche n’importe quel terrain libre hors de la piste pour poser un dispositif (chacun occupe un nombre de cases différent), puis touche-le pour l’améliorer. Deux voies maximum : les deux peuvent atteindre le niveau 2, la première au niveau 3 devient principale jusqu’au 5 ; la spécialisation niv. 6 retire la secondaire et déduit ce que tu y as dépensé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+        </is>
+      </c>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>Tap any free ground off the track to place a device, then tap the device to upgrade it.</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="inlineStr">
+        <is>
+          <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis touchez-le pour l’améliorer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
+        </is>
+      </c>
+      <c r="B302" s="8" t="inlineStr">
+        <is>
+          <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
+        </is>
+      </c>
+      <c r="C302" s="8" t="inlineStr">
+        <is>
+          <t>Tap free ground off the track to place a device, then press “Start wave 1”</t>
+        </is>
+      </c>
+      <c r="D302" s="8" t="inlineStr">
+        <is>
+          <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis « Lancer la vague 1 »</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="10" t="inlineStr">
         <is>
           <t>※ 花括号里的 {n}、{x} 等是占位符，翻译时要原样保留。</t>
         </is>
@@ -19438,10 +19484,10 @@
         <v/>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.451</v>
+        <v>0.419</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="M4" s="14">
         <f>IF(OR(K4="",L4="",L4=0),"",K4/L4)</f>
@@ -19492,10 +19538,10 @@
         <v/>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.515</v>
+        <v>0.468</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0.537</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="M5" s="14">
         <f>IF(OR(K5="",L5="",L5=0),"",K5/L5)</f>
@@ -19550,10 +19596,10 @@
         <v/>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.739</v>
+        <v>0.778</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.82</v>
+        <v>0.793</v>
       </c>
       <c r="M6" s="14">
         <f>IF(OR(K6="",L6="",L6=0),"",K6/L6)</f>
@@ -19604,7 +19650,7 @@
         <v/>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.789</v>
+        <v>0.831</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>1</v>
@@ -19766,10 +19812,10 @@
         <v/>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.282</v>
+        <v>0.267</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.311</v>
+        <v>0.299</v>
       </c>
       <c r="M10" s="14">
         <f>IF(OR(K10="",L10="",L10=0),"",K10/L10)</f>
@@ -19820,10 +19866,10 @@
         <v/>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.306</v>
+        <v>0.31</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.438</v>
+        <v>0.464</v>
       </c>
       <c r="M11" s="14">
         <f>IF(OR(K11="",L11="",L11=0),"",K11/L11)</f>
@@ -19874,10 +19920,10 @@
         <v/>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.403</v>
+        <v>0.378</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.724</v>
+        <v>0.73</v>
       </c>
       <c r="M12" s="14">
         <f>IF(OR(K12="",L12="",L12=0),"",K12/L12)</f>
@@ -19928,10 +19974,10 @@
         <v/>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.376</v>
+        <v>0.441</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1</v>
+        <v>0.959</v>
       </c>
       <c r="M13" s="14">
         <f>IF(OR(K13="",L13="",L13=0),"",K13/L13)</f>
@@ -20086,10 +20132,10 @@
         <v/>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.229</v>
+        <v>0.238</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.321</v>
+        <v>0.312</v>
       </c>
       <c r="M16" s="14">
         <f>IF(OR(K16="",L16="",L16=0),"",K16/L16)</f>
@@ -20140,10 +20186,10 @@
         <v/>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.248</v>
+        <v>0.227</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.501</v>
+        <v>0.523</v>
       </c>
       <c r="M17" s="14">
         <f>IF(OR(K17="",L17="",L17=0),"",K17/L17)</f>
@@ -20198,10 +20244,10 @@
         <v/>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.243</v>
+        <v>0.203</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.82</v>
+        <v>0.793</v>
       </c>
       <c r="M18" s="14">
         <f>IF(OR(K18="",L18="",L18=0),"",K18/L18)</f>
@@ -20256,7 +20302,7 @@
         <v/>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.238</v>
+        <v>0.244</v>
       </c>
       <c r="L19" s="9" t="n">
         <v>1</v>
@@ -20472,10 +20518,10 @@
         <v/>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.451</v>
+        <v>0.424</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.584</v>
+        <v>0.529</v>
       </c>
       <c r="M23" s="14">
         <f>IF(OR(K23="",L23="",L23=0),"",K23/L23)</f>
@@ -20526,10 +20572,10 @@
         <v/>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.514</v>
+        <v>0.444</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.769</v>
+        <v>0.742</v>
       </c>
       <c r="M24" s="14">
         <f>IF(OR(K24="",L24="",L24=0),"",K24/L24)</f>
@@ -20580,10 +20626,10 @@
         <v/>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.981</v>
+        <v>0.988</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.998</v>
+        <v>0.997</v>
       </c>
       <c r="M25" s="14">
         <f>IF(OR(K25="",L25="",L25=0),"",K25/L25)</f>
@@ -20796,10 +20842,10 @@
         <v/>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.417</v>
+        <v>0.444</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.584</v>
+        <v>0.529</v>
       </c>
       <c r="M29" s="14">
         <f>IF(OR(K29="",L29="",L29=0),"",K29/L29)</f>
@@ -20854,10 +20900,10 @@
         <v/>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.579</v>
+        <v>0.569</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.796</v>
+        <v>0.769</v>
       </c>
       <c r="M30" s="14">
         <f>IF(OR(K30="",L30="",L30=0),"",K30/L30)</f>
@@ -20962,7 +21008,7 @@
         <v/>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.725</v>
+        <v>0.78</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>1</v>
@@ -21120,10 +21166,10 @@
         <v/>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.417</v>
+        <v>0.389</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.546</v>
+        <v>0.485</v>
       </c>
       <c r="M35" s="14">
         <f>IF(OR(K35="",L35="",L35=0),"",K35/L35)</f>
@@ -21178,10 +21224,10 @@
         <v/>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.382</v>
+        <v>0.354</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.737</v>
+        <v>0.706</v>
       </c>
       <c r="M36" s="14">
         <f>IF(OR(K36="",L36="",L36=0),"",K36/L36)</f>
@@ -21239,7 +21285,7 @@
         <v>0.326</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.978</v>
+        <v>0.965</v>
       </c>
       <c r="M37" s="14">
         <f>IF(OR(K37="",L37="",L37=0),"",K37/L37)</f>
@@ -21294,7 +21340,7 @@
         <v/>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.667</v>
+        <v>0.646</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>1</v>
@@ -21506,10 +21552,10 @@
         <v/>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.385</v>
+        <v>0.356</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="M42" s="14">
         <f>IF(OR(K42="",L42="",L42=0),"",K42/L42)</f>
@@ -21560,10 +21606,10 @@
         <v/>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.385</v>
+        <v>0.358</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.524</v>
+        <v>0.508</v>
       </c>
       <c r="M43" s="14">
         <f>IF(OR(K43="",L43="",L43=0),"",K43/L43)</f>
@@ -21618,10 +21664,10 @@
         <v/>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.647</v>
+        <v>0.615</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="M44" s="14">
         <f>IF(OR(K44="",L44="",L44=0),"",K44/L44)</f>
@@ -21672,10 +21718,10 @@
         <v/>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.955</v>
+        <v>0.965</v>
       </c>
       <c r="M45" s="14">
         <f>IF(OR(K45="",L45="",L45=0),"",K45/L45)</f>
@@ -21838,10 +21884,10 @@
         <v/>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.255</v>
+        <v>0.257</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="M48" s="14">
         <f>IF(OR(K48="",L48="",L48=0),"",K48/L48)</f>
@@ -21896,10 +21942,10 @@
         <v/>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.329</v>
+        <v>0.351</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.496</v>
+        <v>0.485</v>
       </c>
       <c r="M49" s="14">
         <f>IF(OR(K49="",L49="",L49=0),"",K49/L49)</f>
@@ -21954,10 +22000,10 @@
         <v/>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.633</v>
+        <v>0.695</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="M50" s="14">
         <f>IF(OR(K50="",L50="",L50=0),"",K50/L50)</f>
@@ -22012,10 +22058,10 @@
         <v/>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.605</v>
+        <v>0.619</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.969</v>
+        <v>0.978</v>
       </c>
       <c r="M51" s="14">
         <f>IF(OR(K51="",L51="",L51=0),"",K51/L51)</f>
@@ -22174,10 +22220,10 @@
         <v/>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="M54" s="14">
         <f>IF(OR(K54="",L54="",L54=0),"",K54/L54)</f>
@@ -22228,10 +22274,10 @@
         <v/>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.58</v>
+        <v>0.556</v>
       </c>
       <c r="M55" s="14">
         <f>IF(OR(K55="",L55="",L55=0),"",K55/L55)</f>
@@ -22282,10 +22328,10 @@
         <v/>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.787</v>
+        <v>0.796</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.82</v>
+        <v>0.837</v>
       </c>
       <c r="M56" s="14">
         <f>IF(OR(K56="",L56="",L56=0),"",K56/L56)</f>
@@ -22343,7 +22389,7 @@
         <v>0.604</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.955</v>
+        <v>0.965</v>
       </c>
       <c r="M57" s="14">
         <f>IF(OR(K57="",L57="",L57=0),"",K57/L57)</f>
@@ -22552,10 +22598,10 @@
         <v/>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.308</v>
+        <v>0.253</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>0.302</v>
+        <v>0.292</v>
       </c>
       <c r="M61" s="14">
         <f>IF(OR(K61="",L61="",L61=0),"",K61/L61)</f>
@@ -22606,10 +22652,10 @@
         <v/>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.256</v>
+        <v>0.297</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>0.389</v>
+        <v>0.426</v>
       </c>
       <c r="M62" s="14">
         <f>IF(OR(K62="",L62="",L62=0),"",K62/L62)</f>
@@ -22664,10 +22710,10 @@
         <v/>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.504</v>
+        <v>0.531</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="M63" s="14">
         <f>IF(OR(K63="",L63="",L63=0),"",K63/L63)</f>
@@ -22718,10 +22764,10 @@
         <v/>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.68</v>
+        <v>0.609</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
       <c r="M64" s="14">
         <f>IF(OR(K64="",L64="",L64=0),"",K64/L64)</f>
@@ -22879,7 +22925,7 @@
         <v>0.408</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>0.328</v>
+        <v>0.332</v>
       </c>
       <c r="M67" s="14">
         <f>IF(OR(K67="",L67="",L67=0),"",K67/L67)</f>
@@ -22930,10 +22976,10 @@
         <v/>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.428</v>
+        <v>0.381</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>0.489</v>
+        <v>0.508</v>
       </c>
       <c r="M68" s="14">
         <f>IF(OR(K68="",L68="",L68=0),"",K68/L68)</f>
@@ -22988,10 +23034,10 @@
         <v/>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.336</v>
+        <v>0.408</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>0.724</v>
+        <v>0.745</v>
       </c>
       <c r="M69" s="14">
         <f>IF(OR(K69="",L69="",L69=0),"",K69/L69)</f>
@@ -23046,10 +23092,10 @@
         <v/>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.631</v>
+        <v>0.6</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>1</v>
+        <v>0.945</v>
       </c>
       <c r="M70" s="14">
         <f>IF(OR(K70="",L70="",L70=0),"",K70/L70)</f>
@@ -23200,10 +23246,10 @@
         <v/>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.289</v>
+        <v>0.267</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>0.311</v>
+        <v>0.305</v>
       </c>
       <c r="M73" s="14">
         <f>IF(OR(K73="",L73="",L73=0),"",K73/L73)</f>
@@ -23254,10 +23300,10 @@
         <v/>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.325</v>
+        <v>0.292</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>0.42</v>
+        <v>0.462</v>
       </c>
       <c r="M74" s="14">
         <f>IF(OR(K74="",L74="",L74=0),"",K74/L74)</f>
@@ -23308,10 +23354,10 @@
         <v/>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.342</v>
+        <v>0.267</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="M75" s="14">
         <f>IF(OR(K75="",L75="",L75=0),"",K75/L75)</f>
@@ -23366,10 +23412,10 @@
         <v/>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.3</v>
+        <v>0.289</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>1</v>
+        <v>0.958</v>
       </c>
       <c r="M76" s="14">
         <f>IF(OR(K76="",L76="",L76=0),"",K76/L76)</f>
@@ -23582,10 +23628,10 @@
         <v/>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>0.328</v>
+        <v>0.336</v>
       </c>
       <c r="M80" s="14">
         <f>IF(OR(K80="",L80="",L80=0),"",K80/L80)</f>
@@ -23643,7 +23689,7 @@
         <v>0.379</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>0.447</v>
+        <v>0.461</v>
       </c>
       <c r="M81" s="14">
         <f>IF(OR(K81="",L81="",L81=0),"",K81/L81)</f>
@@ -23694,10 +23740,10 @@
         <v/>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.647</v>
+        <v>0.613</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="M82" s="14">
         <f>IF(OR(K82="",L82="",L82=0),"",K82/L82)</f>
@@ -23748,10 +23794,10 @@
         <v/>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.636</v>
+        <v>0.624</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>1</v>
+        <v>0.964</v>
       </c>
       <c r="M83" s="14">
         <f>IF(OR(K83="",L83="",L83=0),"",K83/L83)</f>
@@ -23910,10 +23956,10 @@
         <v/>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.383</v>
+        <v>0.425</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>0.365</v>
+        <v>0.375</v>
       </c>
       <c r="M86" s="14">
         <f>IF(OR(K86="",L86="",L86=0),"",K86/L86)</f>
@@ -23964,10 +24010,10 @@
         <v/>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.426</v>
+        <v>0.403</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="M87" s="14">
         <f>IF(OR(K87="",L87="",L87=0),"",K87/L87)</f>
@@ -24018,10 +24064,10 @@
         <v/>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.46</v>
+        <v>0.423</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>0.836</v>
+        <v>0.824</v>
       </c>
       <c r="M88" s="14">
         <f>IF(OR(K88="",L88="",L88=0),"",K88/L88)</f>
@@ -24072,10 +24118,10 @@
         <v/>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.593</v>
+        <v>0.602</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>1</v>
+        <v>0.974</v>
       </c>
       <c r="M89" s="14">
         <f>IF(OR(K89="",L89="",L89=0),"",K89/L89)</f>
@@ -24226,10 +24272,10 @@
         <v/>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.272</v>
+        <v>0.256</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>0.335</v>
+        <v>0.344</v>
       </c>
       <c r="M92" s="14">
         <f>IF(OR(K92="",L92="",L92=0),"",K92/L92)</f>
@@ -24284,10 +24330,10 @@
         <v/>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.407</v>
+        <v>0.421</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>0.499</v>
+        <v>0.515</v>
       </c>
       <c r="M93" s="14">
         <f>IF(OR(K93="",L93="",L93=0),"",K93/L93)</f>
@@ -24338,10 +24384,10 @@
         <v/>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.459</v>
+        <v>0.444</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>0.849</v>
+        <v>0.834</v>
       </c>
       <c r="M94" s="14">
         <f>IF(OR(K94="",L94="",L94=0),"",K94/L94)</f>
@@ -24392,7 +24438,7 @@
         <v/>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.593</v>
+        <v>0.611</v>
       </c>
       <c r="L95" s="9" t="n">
         <v>1</v>
@@ -24586,7 +24632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25996,43 +26042,58 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>scoreKill</t>
+          <t>gridTrackGap</t>
         </is>
       </c>
       <c r="B94" s="7" t="n">
-        <v>600</v>
+        <v>24</v>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>分数：劝退率权重</t>
+          <t>放置格子：格子中心离跑道中心线小于这个距离就算跑道，不能放装置</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>scoreLives</t>
+          <t>scoreKill</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>分数：剩余生命权重</t>
+          <t>分数：劝退率权重</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
+          <t>scoreLives</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>分数：剩余生命权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
           <t>scoreClean</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
+      <c r="B97" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>分数：无漏怪波数权重</t>
         </is>
@@ -26050,7 +26111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -26076,6 +26137,7 @@
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="46" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -26194,6 +26256,11 @@
           <t>基础附加效果（写法同「升级」的 effect）</t>
         </is>
       </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>占地（N × N 格，1 格 = 20）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -26311,6 +26378,11 @@
           <t>extra</t>
         </is>
       </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -26406,6 +26478,9 @@
           <t>shots=1</t>
         </is>
       </c>
+      <c r="X3" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -26501,6 +26576,9 @@
           <t>hitCap=4; slip=0.6; peelMax=4; peelLife=8; bombs=1; spread=14</t>
         </is>
       </c>
+      <c r="X4" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -26596,6 +26674,9 @@
           <t>frostNeed=4; freezeCap=99</t>
         </is>
       </c>
+      <c r="X5" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -26691,6 +26772,9 @@
           <t>aimR=46; load=1</t>
         </is>
       </c>
+      <c r="X6" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -26786,6 +26870,9 @@
           <t>hop=70; dizzyDur=1.6</t>
         </is>
       </c>
+      <c r="X7" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -26881,6 +26968,9 @@
           <t>cap=3; stay=1.5</t>
         </is>
       </c>
+      <c r="X8" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -26972,6 +27062,9 @@
         </is>
       </c>
       <c r="W9" s="7" t="inlineStr"/>
+      <c r="X9" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -7145,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>46</v>
+        <v>44.6</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.5</v>
@@ -7958,13 +7958,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A3.png</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A3.json</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>54</v>
+        <v>46.5</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.5</v>
@@ -8007,13 +8015,21 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A6.png</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A6.json</t>
+        </is>
+      </c>
       <c r="G17" s="7" t="n">
-        <v>48</v>
+        <v>62.8</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>58</v>
+        <v>67.2</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.5</v>
@@ -10419,10 +10435,10 @@
         </is>
       </c>
       <c r="G66" s="7" t="n">
-        <v>13</v>
+        <v>19.1</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>13</v>
+        <v>19.1</v>
       </c>
       <c r="I66" s="7" t="n">
         <v>0.5</v>
@@ -10787,57 +10803,513 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>tower.dart.A1</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>装置变种</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>易拉罐投手「重罐点名」1 级挂件：挂一个秤砣</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A1.png</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A1.json</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="9">
+        <f>IF(K74&gt;1,K74*G74*3&amp;" × "&amp;H74*3&amp;"（"&amp;K74&amp;" 帧横排）",G74*3&amp;" × "&amp;H74*3)</f>
+        <v/>
+      </c>
+    </row>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>tower.dart.A2</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>装置变种</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>易拉罐投手「重罐点名」2 级挂件：两侧各挂一个秤砣</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A2.png</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A2.json</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="9">
+        <f>IF(K75&gt;1,K75*G75*3&amp;" × "&amp;H75*3&amp;"（"&amp;K75&amp;" 帧横排）",G75*3&amp;" × "&amp;H75*3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>shot.dart.A3</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>子弹</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>投掷物「重罐点名」3 级：蓄力铜罐</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A3.png</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A3.json</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9">
+        <f>IF(K76&gt;1,K76*G76*3&amp;" × "&amp;H76*3&amp;"（"&amp;K76&amp;" 帧横排）",G76*3&amp;" × "&amp;H76*3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>tower.dart.A4</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>装置变种</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>易拉罐投手「重罐点名」4 级：破防刺罐</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A4.png</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A4.json</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9">
+        <f>IF(K77&gt;1,K77*G77*3&amp;" × "&amp;H77*3&amp;"（"&amp;K77&amp;" 帧横排）",G77*3&amp;" × "&amp;H77*3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>shot.dart.A4</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>子弹</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>投掷物「重罐点名」4 级：破防刺罐</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A4.png</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A4.json</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9">
+        <f>IF(K78&gt;1,K78*G78*3&amp;" × "&amp;H78*3&amp;"（"&amp;K78&amp;" 帧横排）",G78*3&amp;" × "&amp;H78*3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>tower.dart.A5</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>装置变种</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>易拉罐投手「重罐点名」5 级：手雷</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A5.png</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.dart.A5.json</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="9">
+        <f>IF(K79&gt;1,K79*G79*3&amp;" × "&amp;H79*3&amp;"（"&amp;K79&amp;" 帧横排）",G79*3&amp;" × "&amp;H79*3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>shot.dart.A5</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>子弹</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>投掷物「重罐点名」5 级：手雷</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A5.png</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A5.json</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9">
+        <f>IF(K80&gt;1,K80*G80*3&amp;" × "&amp;H80*3&amp;"（"&amp;K80&amp;" 帧横排）",G80*3&amp;" × "&amp;H80*3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>shot.dart.A6</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>子弹</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>投掷物「重罐点名」6 级：双层底座 + 陨石</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A6.png</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.dart.A6.json</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9">
+        <f>IF(K81&gt;1,K81*G81*3&amp;" × "&amp;H81*3&amp;"（"&amp;K81&amp;" 帧横排）",G81*3&amp;" × "&amp;H81*3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>※ 图片地址填公开可访问的 https:// 链接（PNG / WebP，透明背景）；也可以不填，直接在游戏页面点「导入美术图片」，把文件名改成资源编号（如 tower.dart.png）一次选多张。</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>※ 游戏内宽高以 360 × 600 的画布为单位；出图按 3 倍像素（见最后一列），游戏会缩放到这里填的尺寸。</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>※ 锚点是图片里对齐游戏坐标的那一点：0,0 = 左上角，0.5,1 = 底边中点（跑者、装置用脚底中点）。</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>※ 帧数 &gt; 1 时，图片是横向排开的序列帧（每帧等宽），按帧率循环播放。跑者、Boss 统一画成「侧面向右跑」，向左时游戏自动水平翻转。</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>※ 装置变种图 tower.xxx.A3 / A6（B、C 同理）：该路线成为主路线并升到 3 级 / 6 级时替换基础图；没给就往下找，最后用基础图。导入时文件名里的装置也可以写 can / banana / sprinkler / drone / speaker / chill。</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>※ 动画：PNG 精灵图 + 同名 JSON（Aseprite「导出精灵图」勾选 JSON Data，或 TexturePacker JSON）。动画段用 Tag：idle 待机、fire 发射、build 放置、fly 子弹飞行、hit 命中；再用 1 帧的 release Tag 标出子弹离手的那一帧。用 Slice 标点：pivot 脚底 / 中心，muzzle 子弹出手点。导入时把 PNG 和 JSON 一起选上即可，或在「动画 JSON 地址」填链接。</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>※ 子弹只画外观：fly 画朝右，游戏沿弹道自动旋转；弹道类型、速度、抛物线高度在「弹道」表里调。</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>※ 优先级：P1 样板关（先画这些就能完整玩一张图）→ P2 → P3。</t>
         </is>
@@ -10845,7 +11317,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="M3:M73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M3:M81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -7145,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7664,13 +7664,21 @@
           <t>P1 样板关</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.bomb.png</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.bomb.json</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="n">
-        <v>40</v>
+        <v>44.6</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.5</v>
@@ -7713,13 +7721,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.frost.png</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.frost.json</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="n">
-        <v>40</v>
+        <v>78.2</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.5</v>
@@ -7762,13 +7778,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.sniper.png</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.sniper.json</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="n">
-        <v>40</v>
+        <v>48.9</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>50</v>
+        <v>40.5</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.5</v>
@@ -7811,13 +7835,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.tesla.png</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.tesla.json</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="n">
-        <v>40</v>
+        <v>62.3</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>50</v>
+        <v>55.5</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.5</v>
@@ -10481,13 +10513,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.bomb.png</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.bomb.json</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I67" s="7" t="n">
         <v>0.5</v>
@@ -10530,13 +10570,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.sniper.png</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.sniper.json</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="n">
-        <v>16</v>
+        <v>19.1</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>12</v>
+        <v>19.1</v>
       </c>
       <c r="I68" s="7" t="n">
         <v>0.5</v>
@@ -10579,7 +10627,11 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.peel.png</t>
+        </is>
+      </c>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="7" t="n">
         <v>18</v>
@@ -11259,65 +11311,122 @@
         <v/>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>※ 图片地址填公开可访问的 https:// 链接（PNG / WebP，透明背景）；也可以不填，直接在游戏页面点「导入美术图片」，把文件名改成资源编号（如 tower.dart.png）一次选多张。</t>
-        </is>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>fx.drone</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>鞋盒无人机送货飞行（fly 循环，pivot 在机身中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.drone.png</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.drone.json</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9">
+        <f>IF(K82&gt;1,K82*G82*3&amp;" × "&amp;H82*3&amp;"（"&amp;K82&amp;" 帧横排）",G82*3&amp;" × "&amp;H82*3)</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>※ 游戏内宽高以 360 × 600 的画布为单位；出图按 3 倍像素（见最后一列），游戏会缩放到这里填的尺寸。</t>
+          <t>※ 图片地址填公开可访问的 https:// 链接（PNG / WebP，透明背景）；也可以不填，直接在游戏页面点「导入美术图片」，把文件名改成资源编号（如 tower.dart.png）一次选多张。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>※ 锚点是图片里对齐游戏坐标的那一点：0,0 = 左上角，0.5,1 = 底边中点（跑者、装置用脚底中点）。</t>
+          <t>※ 游戏内宽高以 360 × 600 的画布为单位；出图按 3 倍像素（见最后一列），游戏会缩放到这里填的尺寸。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>※ 帧数 &gt; 1 时，图片是横向排开的序列帧（每帧等宽），按帧率循环播放。跑者、Boss 统一画成「侧面向右跑」，向左时游戏自动水平翻转。</t>
+          <t>※ 锚点是图片里对齐游戏坐标的那一点：0,0 = 左上角，0.5,1 = 底边中点（跑者、装置用脚底中点）。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>※ 装置变种图 tower.xxx.A3 / A6（B、C 同理）：该路线成为主路线并升到 3 级 / 6 级时替换基础图；没给就往下找，最后用基础图。导入时文件名里的装置也可以写 can / banana / sprinkler / drone / speaker / chill。</t>
+          <t>※ 帧数 &gt; 1 时，图片是横向排开的序列帧（每帧等宽），按帧率循环播放。跑者、Boss 统一画成「侧面向右跑」，向左时游戏自动水平翻转。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>※ 动画：PNG 精灵图 + 同名 JSON（Aseprite「导出精灵图」勾选 JSON Data，或 TexturePacker JSON）。动画段用 Tag：idle 待机、fire 发射、build 放置、fly 子弹飞行、hit 命中；再用 1 帧的 release Tag 标出子弹离手的那一帧。用 Slice 标点：pivot 脚底 / 中心，muzzle 子弹出手点。导入时把 PNG 和 JSON 一起选上即可，或在「动画 JSON 地址」填链接。</t>
+          <t>※ 装置变种图 tower.xxx.A3 / A6（B、C 同理）：该路线成为主路线并升到 3 级 / 6 级时替换基础图；没给就往下找，最后用基础图。导入时文件名里的装置也可以写 can / banana / sprinkler / drone / speaker / chill。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>※ 子弹只画外观：fly 画朝右，游戏沿弹道自动旋转；弹道类型、速度、抛物线高度在「弹道」表里调。</t>
+          <t>※ 动画：PNG 精灵图 + 同名 JSON（Aseprite「导出精灵图」勾选 JSON Data，或 TexturePacker JSON）。动画段用 Tag：idle 待机、fire 发射、build 放置、fly 子弹飞行、hit 命中；再用 1 帧的 release Tag 标出子弹离手的那一帧。用 Slice 标点：pivot 脚底 / 中心，muzzle 子弹出手点。导入时把 PNG 和 JSON 一起选上即可，或在「动画 JSON 地址」填链接。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
+          <t>※ 子弹只画外观：fly 画朝右，游戏沿弹道自动旋转；弹道类型、速度、抛物线高度在「弹道」表里调。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
           <t>※ 优先级：P1 样板关（先画这些就能完整玩一张图）→ P2 → P3。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="M3:M81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M3:M82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>78.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>43</v>
+        <v>50.5</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.5</v>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -7145,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7664,13 +7664,21 @@
           <t>P1 样板关</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.bomb.png</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.bomb.json</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="n">
-        <v>40</v>
+        <v>44.6</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.5</v>
@@ -7713,13 +7721,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.frost.png</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.frost.json</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="n">
-        <v>40</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.5</v>
@@ -7762,13 +7778,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.sniper.png</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.sniper.json</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="n">
-        <v>40</v>
+        <v>48.9</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>50</v>
+        <v>40.5</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.5</v>
@@ -7811,13 +7835,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.tesla.png</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>art/tower.tesla.json</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="n">
-        <v>40</v>
+        <v>62.3</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>50</v>
+        <v>55.5</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.5</v>
@@ -10481,13 +10513,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.bomb.png</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.bomb.json</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I67" s="7" t="n">
         <v>0.5</v>
@@ -10530,13 +10570,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.sniper.png</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.sniper.json</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="n">
-        <v>16</v>
+        <v>19.1</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>12</v>
+        <v>19.1</v>
       </c>
       <c r="I68" s="7" t="n">
         <v>0.5</v>
@@ -10579,7 +10627,11 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.peel.png</t>
+        </is>
+      </c>
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="7" t="n">
         <v>18</v>
@@ -11259,65 +11311,122 @@
         <v/>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>※ 图片地址填公开可访问的 https:// 链接（PNG / WebP，透明背景）；也可以不填，直接在游戏页面点「导入美术图片」，把文件名改成资源编号（如 tower.dart.png）一次选多张。</t>
-        </is>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>fx.drone</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>鞋盒无人机送货飞行（fly 循环，pivot 在机身中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.drone.png</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.drone.json</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9">
+        <f>IF(K82&gt;1,K82*G82*3&amp;" × "&amp;H82*3&amp;"（"&amp;K82&amp;" 帧横排）",G82*3&amp;" × "&amp;H82*3)</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>※ 游戏内宽高以 360 × 600 的画布为单位；出图按 3 倍像素（见最后一列），游戏会缩放到这里填的尺寸。</t>
+          <t>※ 图片地址填公开可访问的 https:// 链接（PNG / WebP，透明背景）；也可以不填，直接在游戏页面点「导入美术图片」，把文件名改成资源编号（如 tower.dart.png）一次选多张。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>※ 锚点是图片里对齐游戏坐标的那一点：0,0 = 左上角，0.5,1 = 底边中点（跑者、装置用脚底中点）。</t>
+          <t>※ 游戏内宽高以 360 × 600 的画布为单位；出图按 3 倍像素（见最后一列），游戏会缩放到这里填的尺寸。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>※ 帧数 &gt; 1 时，图片是横向排开的序列帧（每帧等宽），按帧率循环播放。跑者、Boss 统一画成「侧面向右跑」，向左时游戏自动水平翻转。</t>
+          <t>※ 锚点是图片里对齐游戏坐标的那一点：0,0 = 左上角，0.5,1 = 底边中点（跑者、装置用脚底中点）。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>※ 装置变种图 tower.xxx.A3 / A6（B、C 同理）：该路线成为主路线并升到 3 级 / 6 级时替换基础图；没给就往下找，最后用基础图。导入时文件名里的装置也可以写 can / banana / sprinkler / drone / speaker / chill。</t>
+          <t>※ 帧数 &gt; 1 时，图片是横向排开的序列帧（每帧等宽），按帧率循环播放。跑者、Boss 统一画成「侧面向右跑」，向左时游戏自动水平翻转。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>※ 动画：PNG 精灵图 + 同名 JSON（Aseprite「导出精灵图」勾选 JSON Data，或 TexturePacker JSON）。动画段用 Tag：idle 待机、fire 发射、build 放置、fly 子弹飞行、hit 命中；再用 1 帧的 release Tag 标出子弹离手的那一帧。用 Slice 标点：pivot 脚底 / 中心，muzzle 子弹出手点。导入时把 PNG 和 JSON 一起选上即可，或在「动画 JSON 地址」填链接。</t>
+          <t>※ 装置变种图 tower.xxx.A3 / A6（B、C 同理）：该路线成为主路线并升到 3 级 / 6 级时替换基础图；没给就往下找，最后用基础图。导入时文件名里的装置也可以写 can / banana / sprinkler / drone / speaker / chill。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>※ 子弹只画外观：fly 画朝右，游戏沿弹道自动旋转；弹道类型、速度、抛物线高度在「弹道」表里调。</t>
+          <t>※ 动画：PNG 精灵图 + 同名 JSON（Aseprite「导出精灵图」勾选 JSON Data，或 TexturePacker JSON）。动画段用 Tag：idle 待机、fire 发射、build 放置、fly 子弹飞行、hit 命中；再用 1 帧的 release Tag 标出子弹离手的那一帧。用 Slice 标点：pivot 脚底 / 中心，muzzle 子弹出手点。导入时把 PNG 和 JSON 一起选上即可，或在「动画 JSON 地址」填链接。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
+          <t>※ 子弹只画外观：fly 画朝右，游戏沿弹道自动旋转；弹道类型、速度、抛物线高度在「弹道」表里调。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
           <t>※ 优先级：P1 样板关（先画这些就能完整玩一张图）→ P2 → P3。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="M3:M81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M3:M82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -1339,32 +1339,32 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>洒水器</t>
+          <t>洒水车</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Sprinkler</t>
+          <t>Truck</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Arroseur</t>
+          <t>Camion</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>解锁洒水器：持续喷水，范围减速</t>
+          <t>解锁洒水车：持续喷水，范围减速</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>Unlock the Sprinkler: keeps spraying, slows an area</t>
+          <t>Unlock the Sprinkler Truck: drives around spraying, slows an area</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Débloque l’Arroseur : arrose en continu et ralentit une zone</t>
+          <t>Débloque le Camion arroseur : il roule en arrosant et ralentit une zone</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -7145,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>洒水器：基础造型，面朝右（朝左时游戏自动翻转）。可做动画：idle 待机 + fire 发射（JSON 标出 release 出手帧和 muzzle 出手点）</t>
+          <t>洒水车取水站：基础造型，面朝右（朝左时游戏自动翻转）。可做动画：idle 待机 + fire 发射（JSON 标出 release 出手帧和 muzzle 出手点）</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>洒水器「喷淋湿地」主路线 3 级起的造型（A3；没有 A4、A5 时沿用 A3）</t>
+          <t>洒水车取水站「喷淋湿地」主路线 3 级起的造型（A3；没有 A4、A5 时沿用 A3）</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>洒水器「喷淋湿地」主路线 6 级起的造型（A6；没有 A4、A5 时沿用 A3）</t>
+          <t>洒水车取水站「喷淋湿地」主路线 6 级起的造型（A6；没有 A4、A5 时沿用 A3）</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>洒水器「寒霜喷头」主路线 3 级起的造型（B3；没有 B4、B5 时沿用 B3）</t>
+          <t>洒水车取水站「寒霜喷头」主路线 3 级起的造型（B3；没有 B4、B5 时沿用 B3）</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>洒水器「寒霜喷头」主路线 6 级起的造型（B6；没有 B4、B5 时沿用 B3）</t>
+          <t>洒水车取水站「寒霜喷头」主路线 6 级起的造型（B6；没有 B4、B5 时沿用 B3）</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>洒水器「高压水柱」主路线 3 级起的造型（C3；没有 C4、C5 时沿用 C3）</t>
+          <t>洒水车取水站「高压水柱」主路线 3 级起的造型（C3；没有 C4、C5 时沿用 C3）</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>洒水器「高压水柱」主路线 6 级起的造型（C6；没有 C4、C5 时沿用 C3）</t>
+          <t>洒水车取水站「高压水柱」主路线 6 级起的造型（C6；没有 C4、C5 时沿用 C3）</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -9752,37 +9752,41 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>pad.empty</t>
+          <t>truck.frost</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>空位</t>
+          <t>装置</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>可放置装置的空位（石台 + 加号）</t>
+          <t>洒水车：会开的车，车头朝右（朝左时游戏自动翻转），地面点在车轮下；静态图即可，行驶时游戏会让它颠簸，喷水从车头喷口出；tower.frost（洒水器）画在它的停车位上当取水站</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr"/>
+          <t>P1 样板关</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>art/truck.frost.png</t>
+        </is>
+      </c>
       <c r="F52" s="8" t="inlineStr"/>
       <c r="G52" s="7" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="I52" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K52" s="7" t="n">
         <v>1</v>
@@ -9801,7 +9805,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>pad.base</t>
+          <t>pad.empty</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -9811,7 +9815,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>装置脚下的底座</t>
+          <t>可放置装置的空位（石台 + 加号）</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -9850,31 +9854,31 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>runner.norm</t>
+          <t>pad.base</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>跑者</t>
+          <t>空位</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>慢跑者，侧面向右跑；横向序列帧</t>
+          <t>装置脚下的底座</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>P1 样板关</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr"/>
       <c r="G54" s="7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I54" s="7" t="n">
         <v>0.5</v>
@@ -9883,10 +9887,10 @@
         <v>1</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -9899,7 +9903,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>runner.arm</t>
+          <t>runner.norm</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -9909,7 +9913,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>耐力跑者（更壮、带护具）</t>
+          <t>慢跑者，侧面向右跑；横向序列帧</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -9920,10 +9924,10 @@
       <c r="E55" s="8" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr"/>
       <c r="G55" s="7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I55" s="7" t="n">
         <v>0.5</v>
@@ -9948,7 +9952,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>runner.mini</t>
+          <t>runner.arm</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -9958,21 +9962,21 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>跑团分裂出的小跑者</t>
+          <t>耐力跑者（更壮、带护具）</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 样板关</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr"/>
       <c r="G56" s="7" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I56" s="7" t="n">
         <v>0.5</v>
@@ -9984,7 +9988,7 @@
         <v>6</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M56" s="7" t="n">
         <v>0</v>
@@ -9997,7 +10001,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>runner.gold</t>
+          <t>runner.mini</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -10007,7 +10011,7 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Aurum 召唤的金甲跑者</t>
+          <t>跑团分裂出的小跑者</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -10018,10 +10022,10 @@
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr"/>
       <c r="G57" s="7" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="I57" s="7" t="n">
         <v>0.5</v>
@@ -10033,7 +10037,7 @@
         <v>6</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>0</v>
@@ -10046,31 +10050,31 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>boss.yawn</t>
+          <t>runner.gold</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>跑者</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Nox（黑猫，九命），侧面向右跑；真人原型需本人同意</t>
+          <t>Aurum 召唤的金甲跑者</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>P1 样板关</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr"/>
       <c r="G58" s="7" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I58" s="7" t="n">
         <v>0.5</v>
@@ -10082,7 +10086,7 @@
         <v>6</v>
       </c>
       <c r="L58" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M58" s="7" t="n">
         <v>0</v>
@@ -10095,7 +10099,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>boss.gilg</t>
+          <t>boss.yawn</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -10105,21 +10109,21 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Aurum，侧面向右跑；真人原型需本人同意</t>
+          <t>Nox（黑猫，九命），侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1 样板关</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr"/>
       <c r="G59" s="7" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="I59" s="7" t="n">
         <v>0.5</v>
@@ -10144,7 +10148,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>boss.king</t>
+          <t>boss.gilg</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -10154,7 +10158,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Slimo，侧面向右跑；真人原型需本人同意</t>
+          <t>Aurum，侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -10193,7 +10197,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>boss.lucas</t>
+          <t>boss.king</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -10203,7 +10207,7 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Rocco，侧面向右跑；真人原型需本人同意</t>
+          <t>Slimo，侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -10242,7 +10246,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>boss.shiti</t>
+          <t>boss.lucas</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -10252,7 +10256,7 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Chuckles，侧面向右跑；真人原型需本人同意</t>
+          <t>Rocco，侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -10291,7 +10295,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>boss.jerry</t>
+          <t>boss.shiti</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -10301,7 +10305,7 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Datto，侧面向右跑；真人原型需本人同意</t>
+          <t>Chuckles，侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -10340,7 +10344,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>boss.pizza</t>
+          <t>boss.jerry</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -10350,7 +10354,7 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Pizza Rider（披萨外卖员），侧面向右跑；真人原型需本人同意</t>
+          <t>Datto，侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -10389,7 +10393,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>boss.overflow</t>
+          <t>boss.pizza</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -10399,7 +10403,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Overflow（溢出怪），侧面向右跑；真人原型需本人同意</t>
+          <t>Pizza Rider（披萨外卖员），侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -10438,17 +10442,17 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>shot.dart</t>
+          <t>boss.overflow</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>子弹</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>易拉罐：fly 飞行循环（画朝右，游戏沿弹道旋转）+ hit 命中</t>
+          <t>Overflow（溢出怪），侧面向右跑；真人原型需本人同意</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -10456,33 +10460,25 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>art/shot.dart.png</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>art/shot.dart.json</t>
-        </is>
-      </c>
+      <c r="E66" s="8" t="inlineStr"/>
+      <c r="F66" s="8" t="inlineStr"/>
       <c r="G66" s="7" t="n">
-        <v>19.1</v>
+        <v>64</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>19.1</v>
+        <v>80</v>
       </c>
       <c r="I66" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L66" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M66" s="7" t="n">
         <v>0</v>
@@ -10495,7 +10491,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>shot.bomb</t>
+          <t>shot.dart</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -10505,7 +10501,7 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>飞行中的香蕉皮：fly + hit（落地）</t>
+          <t>易拉罐：fly 飞行循环（画朝右，游戏沿弹道旋转）+ hit 命中</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -10515,19 +10511,19 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>art/shot.bomb.png</t>
+          <t>art/shot.dart.png</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>art/shot.bomb.json</t>
+          <t>art/shot.dart.json</t>
         </is>
       </c>
       <c r="G67" s="7" t="n">
-        <v>15</v>
+        <v>19.1</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>15</v>
+        <v>19.1</v>
       </c>
       <c r="I67" s="7" t="n">
         <v>0.5</v>
@@ -10552,7 +10548,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>shot.sniper</t>
+          <t>shot.bomb</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -10562,7 +10558,7 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>无人机空投的鞋盒：fly（下落）+ hit（砸地）</t>
+          <t>飞行中的香蕉皮：fly + hit（落地）</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -10572,25 +10568,25 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>art/shot.sniper.png</t>
+          <t>art/shot.bomb.png</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>art/shot.sniper.json</t>
+          <t>art/shot.bomb.json</t>
         </is>
       </c>
       <c r="G68" s="7" t="n">
-        <v>19.1</v>
+        <v>15</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>19.1</v>
+        <v>15</v>
       </c>
       <c r="I68" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K68" s="7" t="n">
         <v>1</v>
@@ -10609,17 +10605,17 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>fx.peel</t>
+          <t>shot.sniper</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>地面效果</t>
+          <t>子弹</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>落在跑道上的香蕉皮</t>
+          <t>无人机空投的鞋盒：fly（下落）+ hit（砸地）</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -10629,21 +10625,25 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>art/fx.peel.png</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr"/>
+          <t>art/shot.sniper.png</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>art/shot.sniper.json</t>
+        </is>
+      </c>
       <c r="G69" s="7" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="I69" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K69" s="7" t="n">
         <v>1</v>
@@ -10662,17 +10662,17 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>icon.wave</t>
+          <t>fx.peel</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>界面图标</t>
+          <t>地面效果</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>顶栏「波次」图标</t>
+          <t>落在跑道上的香蕉皮</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -10680,13 +10680,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.peel.png</t>
+        </is>
+      </c>
       <c r="F70" s="8" t="inlineStr"/>
       <c r="G70" s="7" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I70" s="7" t="n">
         <v>0.5</v>
@@ -10711,7 +10715,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>icon.lives</t>
+          <t>icon.wave</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -10721,7 +10725,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>顶栏「生命」图标（心形）</t>
+          <t>顶栏「波次」图标</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -10760,7 +10764,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>icon.gst</t>
+          <t>icon.lives</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -10770,7 +10774,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>顶栏「GST」图标</t>
+          <t>顶栏「生命」图标（心形）</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -10809,7 +10813,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>icon.score</t>
+          <t>icon.gst</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -10819,7 +10823,7 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>顶栏「分数」图标</t>
+          <t>顶栏「GST」图标</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -10858,17 +10862,17 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>tower.dart.A1</t>
+          <t>icon.score</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>装置变种</t>
+          <t>界面图标</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>易拉罐投手「重罐点名」1 级挂件：挂一个秤砣</t>
+          <t>顶栏「分数」图标</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -10876,27 +10880,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>art/tower.dart.A1.png</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>art/tower.dart.A1.json</t>
-        </is>
-      </c>
+      <c r="E74" s="8" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr"/>
       <c r="G74" s="7" t="n">
-        <v>44.6</v>
+        <v>38</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>46.5</v>
+        <v>38</v>
       </c>
       <c r="I74" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="K74" s="7" t="n">
         <v>1</v>
@@ -10915,7 +10911,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>tower.dart.A2</t>
+          <t>tower.dart.A1</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -10925,7 +10921,7 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>易拉罐投手「重罐点名」2 级挂件：两侧各挂一个秤砣</t>
+          <t>易拉罐投手「重罐点名」1 级挂件：挂一个秤砣</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -10935,12 +10931,12 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>art/tower.dart.A2.png</t>
+          <t>art/tower.dart.A1.png</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>art/tower.dart.A2.json</t>
+          <t>art/tower.dart.A1.json</t>
         </is>
       </c>
       <c r="G75" s="7" t="n">
@@ -10972,17 +10968,17 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>shot.dart.A3</t>
+          <t>tower.dart.A2</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>子弹</t>
+          <t>装置变种</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>投掷物「重罐点名」3 级：蓄力铜罐</t>
+          <t>易拉罐投手「重罐点名」2 级挂件：两侧各挂一个秤砣</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -10992,25 +10988,25 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A3.png</t>
+          <t>art/tower.dart.A2.png</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A3.json</t>
+          <t>art/tower.dart.A2.json</t>
         </is>
       </c>
       <c r="G76" s="7" t="n">
-        <v>21.2</v>
+        <v>44.6</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>21.2</v>
+        <v>46.5</v>
       </c>
       <c r="I76" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="K76" s="7" t="n">
         <v>1</v>
@@ -11029,17 +11025,17 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>tower.dart.A4</t>
+          <t>shot.dart.A3</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>装置变种</t>
+          <t>子弹</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>易拉罐投手「重罐点名」4 级：破防刺罐</t>
+          <t>投掷物「重罐点名」3 级：蓄力铜罐</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -11049,25 +11045,25 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>art/tower.dart.A4.png</t>
+          <t>art/shot.dart.A3.png</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>art/tower.dart.A4.json</t>
+          <t>art/shot.dart.A3.json</t>
         </is>
       </c>
       <c r="G77" s="7" t="n">
-        <v>44.6</v>
+        <v>21.2</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>46.5</v>
+        <v>21.2</v>
       </c>
       <c r="I77" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J77" s="7" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="K77" s="7" t="n">
         <v>1</v>
@@ -11086,17 +11082,17 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>shot.dart.A4</t>
+          <t>tower.dart.A4</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>子弹</t>
+          <t>装置变种</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>投掷物「重罐点名」4 级：破防刺罐</t>
+          <t>易拉罐投手「重罐点名」4 级：破防刺罐</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -11106,25 +11102,25 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A4.png</t>
+          <t>art/tower.dart.A4.png</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A4.json</t>
+          <t>art/tower.dart.A4.json</t>
         </is>
       </c>
       <c r="G78" s="7" t="n">
-        <v>21</v>
+        <v>44.6</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>21</v>
+        <v>46.5</v>
       </c>
       <c r="I78" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J78" s="7" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="K78" s="7" t="n">
         <v>1</v>
@@ -11143,17 +11139,17 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>tower.dart.A5</t>
+          <t>shot.dart.A4</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>装置变种</t>
+          <t>子弹</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>易拉罐投手「重罐点名」5 级：手雷</t>
+          <t>投掷物「重罐点名」4 级：破防刺罐</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -11163,25 +11159,25 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>art/tower.dart.A5.png</t>
+          <t>art/shot.dart.A4.png</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>art/tower.dart.A5.json</t>
+          <t>art/shot.dart.A4.json</t>
         </is>
       </c>
       <c r="G79" s="7" t="n">
-        <v>44.6</v>
+        <v>21</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>46.5</v>
+        <v>21</v>
       </c>
       <c r="I79" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="K79" s="7" t="n">
         <v>1</v>
@@ -11200,17 +11196,17 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>shot.dart.A5</t>
+          <t>tower.dart.A5</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>子弹</t>
+          <t>装置变种</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>投掷物「重罐点名」5 级：手雷</t>
+          <t>易拉罐投手「重罐点名」5 级：手雷</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -11220,25 +11216,25 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A5.png</t>
+          <t>art/tower.dart.A5.png</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A5.json</t>
+          <t>art/tower.dart.A5.json</t>
         </is>
       </c>
       <c r="G80" s="7" t="n">
-        <v>23.4</v>
+        <v>44.6</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>23.4</v>
+        <v>46.5</v>
       </c>
       <c r="I80" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="K80" s="7" t="n">
         <v>1</v>
@@ -11257,7 +11253,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>shot.dart.A6</t>
+          <t>shot.dart.A5</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -11267,7 +11263,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>投掷物「重罐点名」6 级：双层底座 + 陨石</t>
+          <t>投掷物「重罐点名」5 级：手雷</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -11277,19 +11273,19 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A6.png</t>
+          <t>art/shot.dart.A5.png</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>art/shot.dart.A6.json</t>
+          <t>art/shot.dart.A5.json</t>
         </is>
       </c>
       <c r="G81" s="7" t="n">
-        <v>42.9</v>
+        <v>23.4</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>42.9</v>
+        <v>23.4</v>
       </c>
       <c r="I81" s="7" t="n">
         <v>0.5</v>
@@ -11314,17 +11310,17 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>fx.drone</t>
+          <t>shot.dart.A6</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>子弹</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>鞋盒无人机送货飞行（fly 循环，pivot 在机身中心）</t>
+          <t>投掷物「重罐点名」6 级：双层底座 + 陨石</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -11334,19 +11330,19 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>art/fx.drone.png</t>
+          <t>art/shot.dart.A6.png</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>art/fx.drone.json</t>
+          <t>art/shot.dart.A6.json</t>
         </is>
       </c>
       <c r="G82" s="7" t="n">
-        <v>48.9</v>
+        <v>42.9</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>33.2</v>
+        <v>42.9</v>
       </c>
       <c r="I82" s="7" t="n">
         <v>0.5</v>
@@ -11368,65 +11364,122 @@
         <v/>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>※ 图片地址填公开可访问的 https:// 链接（PNG / WebP，透明背景）；也可以不填，直接在游戏页面点「导入美术图片」，把文件名改成资源编号（如 tower.dart.png）一次选多张。</t>
-        </is>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>fx.drone</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>鞋盒无人机送货飞行（fly 循环，pivot 在机身中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.drone.png</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>art/fx.drone.json</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J83" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9">
+        <f>IF(K83&gt;1,K83*G83*3&amp;" × "&amp;H83*3&amp;"（"&amp;K83&amp;" 帧横排）",G83*3&amp;" × "&amp;H83*3)</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>※ 游戏内宽高以 360 × 600 的画布为单位；出图按 3 倍像素（见最后一列），游戏会缩放到这里填的尺寸。</t>
+          <t>※ 图片地址填公开可访问的 https:// 链接（PNG / WebP，透明背景）；也可以不填，直接在游戏页面点「导入美术图片」，把文件名改成资源编号（如 tower.dart.png）一次选多张。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>※ 锚点是图片里对齐游戏坐标的那一点：0,0 = 左上角，0.5,1 = 底边中点（跑者、装置用脚底中点）。</t>
+          <t>※ 游戏内宽高以 360 × 600 的画布为单位；出图按 3 倍像素（见最后一列），游戏会缩放到这里填的尺寸。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>※ 帧数 &gt; 1 时，图片是横向排开的序列帧（每帧等宽），按帧率循环播放。跑者、Boss 统一画成「侧面向右跑」，向左时游戏自动水平翻转。</t>
+          <t>※ 锚点是图片里对齐游戏坐标的那一点：0,0 = 左上角，0.5,1 = 底边中点（跑者、装置用脚底中点）。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>※ 装置变种图 tower.xxx.A3 / A6（B、C 同理）：该路线成为主路线并升到 3 级 / 6 级时替换基础图；没给就往下找，最后用基础图。导入时文件名里的装置也可以写 can / banana / sprinkler / drone / speaker / chill。</t>
+          <t>※ 帧数 &gt; 1 时，图片是横向排开的序列帧（每帧等宽），按帧率循环播放。跑者、Boss 统一画成「侧面向右跑」，向左时游戏自动水平翻转。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>※ 动画：PNG 精灵图 + 同名 JSON（Aseprite「导出精灵图」勾选 JSON Data，或 TexturePacker JSON）。动画段用 Tag：idle 待机、fire 发射、build 放置、fly 子弹飞行、hit 命中；再用 1 帧的 release Tag 标出子弹离手的那一帧。用 Slice 标点：pivot 脚底 / 中心，muzzle 子弹出手点。导入时把 PNG 和 JSON 一起选上即可，或在「动画 JSON 地址」填链接。</t>
+          <t>※ 装置变种图 tower.xxx.A3 / A6（B、C 同理）：该路线成为主路线并升到 3 级 / 6 级时替换基础图；没给就往下找，最后用基础图。导入时文件名里的装置也可以写 can / banana / sprinkler / drone / speaker / chill。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>※ 子弹只画外观：fly 画朝右，游戏沿弹道自动旋转；弹道类型、速度、抛物线高度在「弹道」表里调。</t>
+          <t>※ 动画：PNG 精灵图 + 同名 JSON（Aseprite「导出精灵图」勾选 JSON Data，或 TexturePacker JSON）。动画段用 Tag：idle 待机、fire 发射、build 放置、fly 子弹飞行、hit 命中；再用 1 帧的 release Tag 标出子弹离手的那一帧。用 Slice 标点：pivot 脚底 / 中心，muzzle 子弹出手点。导入时把 PNG 和 JSON 一起选上即可，或在「动画 JSON 地址」填链接。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
+          <t>※ 子弹只画外观：fly 画朝右，游戏沿弹道自动旋转；弹道类型、速度、抛物线高度在「弹道」表里调。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
           <t>※ 优先级：P1 样板关（先画这些就能完整玩一张图）→ P2 → P3。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="M3:M82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M3:M83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11699,7 +11752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D304"/>
+  <dimension ref="A1:D303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -11777,22 +11830,22 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>6 种装置：易拉罐投手（单体）、香蕉皮投手（范围滑倒）、洒水器（减速、冻结）、鞋盒无人机（全图空投）、广场舞音响（神曲连锁传播）、宝石发射器（红黄蓝三种宝石）。每种 3 条路线、每条 5 级；主路线可升满，次路线最多 2 级。</t>
+          <t>6 种装置 + 矿机：易拉罐投手（单体）、香蕉皮投手（跑道陷阱、滑倒）、洒水车（会自己开，减速、冻结）、鞋盒无人机（全图空投）、广场舞音响（神曲连锁传播）、休闲诱惑站（把跑者留住）；矿机负责挣钱。每种 3 条路线，最多点 2 条；先到 3 级的成为主路线，可一直升到 6 级。</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>6 种装置：易拉罐投手（单体）、香蕉皮投手（范围滑倒）、洒水器（减速、冻结）、鞋盒无人机（全图空投）、广场舞音响（神曲连锁传播）、宝石发射器（红黄蓝三种宝石）。每种 3 条路线、每条 5 级；主路线可升满，次路线最多 2 级。</t>
+          <t>6 种装置 + 矿机：易拉罐投手（单体）、香蕉皮投手（跑道陷阱、滑倒）、洒水车（会自己开，减速、冻结）、鞋盒无人机（全图空投）、广场舞音响（神曲连锁传播）、休闲诱惑站（把跑者留住）；矿机负责挣钱。每种 3 条路线，最多点 2 条；先到 3 级的成为主路线，可一直升到 6 级。</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>6 devices: Can Thrower (single target), Banana Peeler (area slip), Sprinkler (slow, freeze), Shoebox Drone (map-wide drop), Dance Speaker (chain earworm), Gem Launcher (ruby, topaz, sapphire). Each has 3 paths of 5 tiers; the main path can max out, the secondary stops at tier 2.</t>
+          <t>6 devices plus the miner: Can Thrower (single target), Banana Peeler (track traps, slips), Sprinkler Truck (drives itself; slows, freezes), Shoebox Drone (map-wide drops), Dance Speaker (chain earworm), Chill Spot (holds runners up); the miner earns money. Each has 3 paths and you can take 2; the first to tier 3 becomes the main path and goes up to tier 6.</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>6 dispositifs : Lanceur de canettes (cible unique), Lanceur de peaux de banane (glissade de zone), Arroseur (ralentit, gèle), Drone à boîtes (largage sur toute la carte), Enceinte de danse (tube viral en chaîne), Lance-gemmes (rubis, topaze, saphir). Chacun a 3 voies de 5 niveaux ; la voie principale peut être maximisée, la secondaire s’arrête au niveau 2.</t>
+          <t>6 dispositifs plus le Mineur : Lanceur de canettes (cible unique), Lanceur de peaux de banane (pièges sur la piste, glissades), Camion arroseur (roule tout seul ; ralentit, gèle), Drone à boîtes (largages sur toute la carte), Enceinte de danse (tube viral en chaîne), Coin détente (retient les coureurs) ; le Mineur rapporte de l’argent. Chacun a 3 voies, on peut en prendre 2 ; la première au niveau 3 devient la voie principale et monte jusqu’au niveau 6.</t>
         </is>
       </c>
     </row>
@@ -13163,66 +13216,66 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>次路线</t>
+          <t>每波结束开启神秘箱三选一：宝石、GST 红包、GMT 质押、MOOAR 折扣、Gas Hero 毒气、升级卷轴、创世鞋等。局内 GST 只是关卡内货币，不和任何真实资产挂钩。</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>次路线</t>
+          <t>每波结束开启神秘箱三选一：宝石、GST 红包、GMT 质押、MOOAR 折扣、Gas Hero 毒气、升级卷轴、创世鞋等。局内 GST 只是关卡内货币，不和任何真实资产挂钩。</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>After each wave, open a Mystery Box and pick 1 of 3: gems, GST Red Packets, GMT Staking, MOOAR Discount, Gas Hero Gas, Level-up Scrolls, Genesis Sneakers and more. In-run GST is a level-only currency and is not tied to any real asset.</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Secondaire</t>
+          <t>Après chaque vague, ouvre une Mystery Box et choisis 1 carte sur 3 : gemmes, Enveloppes GST, Staking GMT, Remise MOOAR, Gaz Gas Hero, Parchemins, Sneakers Genesis, etc. Le GST de la partie est une monnaie de niveau, sans lien avec un actif réel.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>每波结束开启神秘箱三选一：宝石、GST 红包、GMT 质押、MOOAR 折扣、Gas Hero 毒气、升级卷轴、创世鞋等。局内 GST 只是关卡内货币，不和任何真实资产挂钩。</t>
+          <t>波次</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>每波结束开启神秘箱三选一：宝石、GST 红包、GMT 质押、MOOAR 折扣、Gas Hero 毒气、升级卷轴、创世鞋等。局内 GST 只是关卡内货币，不和任何真实资产挂钩。</t>
+          <t>波次</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>After each wave, open a Mystery Box and pick 1 of 3: gems, GST Red Packets, GMT Staking, MOOAR Discount, Gas Hero Gas, Level-up Scrolls, Genesis Sneakers and more. In-run GST is a level-only currency and is not tied to any real asset.</t>
+          <t>Wave</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Après chaque vague, ouvre une Mystery Box et choisis 1 carte sur 3 : gemmes, Enveloppes GST, Staking GMT, Remise MOOAR, Gaz Gas Hero, Parchemins, Sneakers Genesis, etc. Le GST de la partie est une monnaie de niveau, sans lien avec un actif réel.</t>
+          <t>Vague</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>波次</t>
+          <t>活动范围</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>波次</t>
+          <t>活动范围</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Wave</t>
+          <t>Patrol</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Vague</t>
+          <t>Patrouille</t>
         </is>
       </c>
     </row>
@@ -15935,2425 +15988,2403 @@
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>宝石发射器</t>
+          <t>红宝石</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>宝石发射器</t>
+          <t>红宝石</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Gem Launcher</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Lance-gemmes</t>
+          <t>Rubis</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>红宝石</t>
+          <t>蓝宝石</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>红宝石</t>
+          <t>蓝宝石</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Sapphire</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Rubis</t>
+          <t>Saphir</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>蓝宝石</t>
+          <t>下一级：{x}</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>蓝宝石</t>
+          <t>下一级：{x}</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Sapphire</t>
+          <t>Next: {x}</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Saphir</t>
+          <t>Suivant : {x}</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>下一级：{x}</t>
+          <t>这里不能放</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>下一级：{x}</t>
+          <t>这里不能放</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Next: {x}</t>
+          <t>Can’t build here</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Suivant : {x}</t>
+          <t>Impossible ici</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>这里不能放</t>
+          <t>取消放置</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>这里不能放</t>
+          <t>取消放置</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Can’t build here</t>
+          <t>Cancel placing</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Impossible ici</t>
+          <t>Annuler</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>取消放置</t>
+          <t>＋ 放置点 ×{n}</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>取消放置</t>
+          <t>＋ 放置点 ×{n}</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Cancel placing</t>
+          <t>+ Spot ×{n}</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>+ Emplacement ×{n}</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>＋ 放置点 ×{n}</t>
+          <t>点跑道外的空地，新增一个放置点</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>＋ 放置点 ×{n}</t>
+          <t>点跑道外的空地，新增一个放置点</t>
         </is>
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>+ Spot ×{n}</t>
+          <t>Tap open ground off the track to add a spot</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>+ Emplacement ×{n}</t>
+          <t>Touche un terrain libre hors piste pour ajouter un emplacement</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>点跑道外的空地，新增一个放置点</t>
+          <t>聪</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>点跑道外的空地，新增一个放置点</t>
+          <t>聪</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Tap open ground off the track to add a spot</t>
+          <t>sats</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Touche un terrain libre hors piste pour ajouter un emplacement</t>
+          <t>sats</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>聪</t>
+          <t>创世纪 · 2008–2010</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>聪</t>
+          <t>创世纪 · 2008–2010</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>sats</t>
+          <t>Genesis · 2008–2010</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>sats</t>
+          <t>Genèse · 2008–2010</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>创世纪 · 2008–2010</t>
+          <t>组合</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>创世纪 · 2008–2010</t>
+          <t>组合</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Genesis · 2008–2010</t>
+          <t>Combos</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Genèse · 2008–2010</t>
+          <t>Combos</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>组合</t>
+          <t>重试</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>组合</t>
+          <t>重试</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>Combos</t>
+          <t>Retry</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Combos</t>
+          <t>Réessayer</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>重试</t>
+          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>重试</t>
+          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Retry</t>
+          <t>A STEPN runner falls into a blockchain time tunnel and lives through bitcoin’s first three years.</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Réessayer</t>
+          <t>Un coureur STEPN tombe dans un tunnel temporel blockchain et vit les trois premières années du bitcoin.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
+          <t>累计积分 {n}</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>STEPN 跑者掉进区块链时光隧道，跟着比特币走过最初的三年。</t>
+          <t>累计积分 {n}</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
         <is>
-          <t>A STEPN runner falls into a blockchain time tunnel and lives through bitcoin’s first three years.</t>
+          <t>Points: {n}</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>Un coureur STEPN tombe dans un tunnel temporel blockchain et vit les trois premières années du bitcoin.</t>
+          <t>Points : {n}</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>累计积分 {n}</t>
+          <t>剧情中…</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>累计积分 {n}</t>
+          <t>剧情中…</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Points: {n}</t>
+          <t>Story…</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Points : {n}</t>
+          <t>Histoire…</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>剧情中…</t>
+          <t>关卡完成</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>剧情中…</t>
+          <t>关卡完成</t>
         </is>
       </c>
       <c r="C207" s="8" t="inlineStr">
         <is>
-          <t>Story…</t>
+          <t>Level complete</t>
         </is>
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>Histoire…</t>
+          <t>Niveau terminé</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>关卡完成</t>
+          <t>再玩一次</t>
         </is>
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>关卡完成</t>
+          <t>再玩一次</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Level complete</t>
+          <t>Play again</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Niveau terminé</t>
+          <t>Rejouer</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>再玩一次</t>
+          <t>章节地图</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>再玩一次</t>
+          <t>章节地图</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>Play again</t>
+          <t>Chapter map</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Rejouer</t>
+          <t>Carte du chapitre</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>章节地图</t>
+          <t>第二章 · 敬请期待</t>
         </is>
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>章节地图</t>
+          <t>第二章 · 敬请期待</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Chapter map</t>
+          <t>Chapter 2 · coming soon</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Carte du chapitre</t>
+          <t>Chapitre 2 · bientôt</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>第二章 · 敬请期待</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>第二章 · 敬请期待</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>Chapter 2 · coming soon</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Chapitre 2 · bientôt</t>
+          <t>Codex</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>区块高度</t>
         </is>
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>图鉴</t>
+          <t>区块高度</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Block height</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Hauteur</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>区块高度</t>
+          <t>区块奖励：选一个，比赛马上继续。</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>区块高度</t>
+          <t>区块奖励：选一个，比赛马上继续。</t>
         </is>
       </c>
       <c r="C213" s="8" t="inlineStr">
         <is>
-          <t>Block height</t>
+          <t>Block reward: pick one and the race resumes.</t>
         </is>
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>Hauteur</t>
+          <t>Récompense de bloc : choisis-en une et la course reprend.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>区块奖励：选一个，比赛马上继续。</t>
+          <t>选择关卡</t>
         </is>
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>区块奖励：选一个，比赛马上继续。</t>
+          <t>选择关卡</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Block reward: pick one and the race resumes.</t>
+          <t>Choose a level</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Récompense de bloc : choisis-en une et la course reprend.</t>
+          <t>Choisir un niveau</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>选择关卡</t>
+          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>选择关卡</t>
+          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="C215" s="8" t="inlineStr">
         <is>
-          <t>Choose a level</t>
+          <t>No combos this time. Try stacking two statuses on the same runner.</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Choisir un niveau</t>
+          <t>Aucun combo cette fois. Essaie de cumuler deux états sur le même coureur.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
+          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
         </is>
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>这关还没打出组合，试试把两种状态叠在同一个跑者身上。</t>
+          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>No combos this time. Try stacking two statuses on the same runner.</t>
+          <t>Keys: Space start wave · F speed · 1–7 build · Q/W/E upgrade · X recycle · Esc cancel</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Aucun combo cette fois. Essaie de cumuler deux états sur le même coureur.</t>
+          <t>Touches : Espace vague · F vitesse · 1–7 construire · Q/W/E améliorer · X recycler · Échap annuler</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
+          <t>一万枚换两个披萨！</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>快捷键：空格 开波 · F 切换速度 · 1–7 建造 · Q/W/E 升级 · X 回收 · Esc 取消</t>
+          <t>一万枚换两个披萨！</t>
         </is>
       </c>
       <c r="C217" s="8" t="inlineStr">
         <is>
-          <t>Keys: Space start wave · F speed · 1–7 build · Q/W/E upgrade · X recycle · Esc cancel</t>
+          <t>10,000 coins for two pizzas!</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Touches : Espace vague · F vitesse · 1–7 construire · Q/W/E améliorer · X recycler · Échap annuler</t>
+          <t>10 000 pièces pour deux pizzas !</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>一万枚换两个披萨！</t>
+          <t>知识卡</t>
         </is>
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>一万枚换两个披萨！</t>
+          <t>知识卡</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>10,000 coins for two pizzas!</t>
+          <t>Knowledge</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>10 000 pièces pour deux pizzas !</t>
+          <t>Savoir</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>知识卡</t>
+          <t>新组合：{x}！</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>知识卡</t>
+          <t>新组合：{x}！</t>
         </is>
       </c>
       <c r="C219" s="8" t="inlineStr">
         <is>
-          <t>Knowledge</t>
+          <t>New combo: {x}!</t>
         </is>
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Savoir</t>
+          <t>Nouveau combo : {x} !</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>新组合：{x}！</t>
+          <t>下一关</t>
         </is>
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>新组合：{x}！</t>
+          <t>下一关</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>New combo: {x}!</t>
+          <t>Next level</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Nouveau combo : {x} !</t>
+          <t>Niveau suivant</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>下一关</t>
+          <t>{n}× 速度</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>下一关</t>
+          <t>{n}× 速度</t>
         </is>
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>Next level</t>
+          <t>{n}× speed</t>
         </is>
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Niveau suivant</t>
+          <t>Vitesse ×{n}</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>{n}× 速度</t>
+          <t>区块 #{h} 被别的矿工抢先挖到了</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>{n}× 速度</t>
+          <t>区块 #{h} 被别的矿工抢先挖到了</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>{n}× speed</t>
+          <t>Block #{h} went to another miner</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Vitesse ×{n}</t>
+          <t>Le bloc #{h} est allé à un autre mineur</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>区块 #{h} 被别的矿工抢先挖到了</t>
+          <t>挖到区块</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>区块 #{h} 被别的矿工抢先挖到了</t>
+          <t>挖到区块</t>
         </is>
       </c>
       <c r="C223" s="8" t="inlineStr">
         <is>
-          <t>Block #{h} went to another miner</t>
+          <t>Blocks mined</t>
         </is>
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Le bloc #{h} est allé à un autre mineur</t>
+          <t>Blocs minés</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>挖到区块</t>
+          <t>本关触发的组合</t>
         </is>
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>挖到区块</t>
+          <t>本关触发的组合</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>Blocks mined</t>
+          <t>Combos this level</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Blocs minés</t>
+          <t>Combos de ce niveau</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>本关触发的组合</t>
+          <t>组合：{x}</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>本关触发的组合</t>
+          <t>组合：{x}</t>
         </is>
       </c>
       <c r="C225" s="8" t="inlineStr">
         <is>
-          <t>Combos this level</t>
+          <t>Combos: {x}</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Combos de ce niveau</t>
+          <t>Combos : {x}</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>组合：{x}</t>
+          <t>修复版本上线，溢出的币被回滚</t>
         </is>
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>组合：{x}</t>
+          <t>修复版本上线，溢出的币被回滚</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Combos: {x}</t>
+          <t>The fix is live; the overflowed coins are rolled back</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Combos : {x}</t>
+          <t>Le correctif est en ligne ; les pièces en trop sont annulées</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>修复版本上线，溢出的币被回滚</t>
+          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>修复版本上线，溢出的币被回滚</t>
+          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
         </is>
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>The fix is live; the overflowed coins are rolled back</t>
+          <t>Not triggered yet. Try stacking these two statuses on one runner.</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Le correctif est en ligne ; les pièces en trop sont annulées</t>
+          <t>Pas encore déclenché. Cumule ces deux états sur un coureur.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
+          <t>出块！#{h}</t>
         </is>
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>还没触发过。试试把这两种状态叠在同一个跑者身上。</t>
+          <t>出块！#{h}</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Not triggered yet. Try stacking these two statuses on one runner.</t>
+          <t>Block! #{h}</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Pas encore déclenché. Cumule ces deux états sur un coureur.</t>
+          <t>Bloc ! #{h}</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>出块！#{h}</t>
+          <t>挖到区块 #{h}！</t>
         </is>
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>出块！#{h}</t>
+          <t>挖到区块 #{h}！</t>
         </is>
       </c>
       <c r="C229" s="8" t="inlineStr">
         <is>
-          <t>Block! #{h}</t>
+          <t>Mined block #{h}!</t>
         </is>
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>Bloc ! #{h}</t>
+          <t>Bloc #{h} miné !</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>挖到区块 #{h}！</t>
+          <t>披萨跑者冲出来了</t>
         </is>
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>挖到区块 #{h}！</t>
+          <t>披萨跑者冲出来了</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Mined block #{h}!</t>
+          <t>Pizza runners incoming</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Bloc #{h} miné !</t>
+          <t>Les coureurs-pizza arrivent</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>披萨跑者冲出来了</t>
+          <t>重抽 · {n} 聪</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>披萨跑者冲出来了</t>
+          <t>重抽 · {n} 聪</t>
         </is>
       </c>
       <c r="C231" s="8" t="inlineStr">
         <is>
-          <t>Pizza runners incoming</t>
+          <t>Reroll · {n} sats</t>
         </is>
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>Les coureurs-pizza arrivent</t>
+          <t>Relancer · {n} sats</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>重抽 · {n} 聪</t>
+          <t>继续 ▶</t>
         </is>
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>重抽 · {n} 聪</t>
+          <t>继续 ▶</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Reroll · {n} sats</t>
+          <t>Next ▶</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Relancer · {n} sats</t>
+          <t>Suite ▶</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>继续 ▶</t>
+          <t>收入图鉴</t>
         </is>
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>继续 ▶</t>
+          <t>收入图鉴</t>
         </is>
       </c>
       <c r="C233" s="8" t="inlineStr">
         <is>
-          <t>Next ▶</t>
+          <t>Add to codex</t>
         </is>
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Suite ▶</t>
+          <t>Ajouter au codex</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>收入图鉴</t>
+          <t>返回章节地图</t>
         </is>
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>收入图鉴</t>
+          <t>返回章节地图</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Add to codex</t>
+          <t>Back to chapter map</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Ajouter au codex</t>
+          <t>Retour à la carte</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>返回章节地图</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>返回章节地图</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
-          <t>Back to chapter map</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Retour à la carte</t>
+          <t>Passer</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>经典模式</t>
         </is>
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>经典模式</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Classic mode</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Passer</t>
+          <t>Mode classique</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>经典模式</t>
+          <t>开始！</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>经典模式</t>
+          <t>开始！</t>
         </is>
       </c>
       <c r="C237" s="8" t="inlineStr">
         <is>
-          <t>Classic mode</t>
+          <t>Go!</t>
         </is>
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>Mode classique</t>
+          <t>C’est parti !</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>开始！</t>
+          <t>算力 {h} · 出块奖励 +{b}%</t>
         </is>
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>开始！</t>
+          <t>算力 {h} · 出块奖励 +{b}%</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Go!</t>
+          <t>Hash {h} · block reward +{b}%</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>C’est parti !</t>
+          <t>Puissance {h} · récompense +{b} %</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>算力 {h} · 出块奖励 +{b}%</t>
+          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
         </is>
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>算力 {h} · 出块奖励 +{b}%</t>
+          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
         </is>
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
-          <t>Hash {h} · block reward +{b}%</t>
+          <t>The network makes a block every dozen seconds or so. Your share of total hash power is your chance of winning it. Win a block: sats plus a pick-one-of-three.</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>Puissance {h} · récompense +{b} %</t>
+          <t>Le réseau produit un bloc toutes les quinze secondes environ. Ta part de la puissance totale est ta chance de le gagner. Bloc gagné : des sats et un choix parmi trois.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
+          <t>出块几率</t>
         </is>
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>全网每隔十几秒出一个区块，你的算力占全网的比例，就是抢到它的几率。挖到区块：得聪，再开一次三选一。</t>
+          <t>出块几率</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>The network makes a block every dozen seconds or so. Your share of total hash power is your chance of winning it. Win a block: sats plus a pick-one-of-three.</t>
+          <t>Win chance</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Le réseau produit un bloc toutes les quinze secondes environ. Ta part de la puissance totale est ta chance de le gagner. Bloc gagné : des sats et un choix parmi trois.</t>
+          <t>Chance</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>出块几率</t>
+          <t>软分叉！</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>出块几率</t>
+          <t>软分叉！</t>
         </is>
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>Win chance</t>
+          <t>Soft fork!</t>
         </is>
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>Chance</t>
+          <t>Soft fork !</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>软分叉！</t>
+          <t>原型阶段的链下积分，没有任何实际价值</t>
         </is>
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>软分叉！</t>
+          <t>原型阶段的链下积分，没有任何实际价值</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Soft fork!</t>
+          <t>off-chain prototype points with no real-world value</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>Soft fork !</t>
+          <t>points hors chaîne du prototype, sans valeur réelle</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>原型阶段的链下积分，没有任何实际价值</t>
+          <t>你的算力</t>
         </is>
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>原型阶段的链下积分，没有任何实际价值</t>
+          <t>你的算力</t>
         </is>
       </c>
       <c r="C243" s="8" t="inlineStr">
         <is>
-          <t>off-chain prototype points with no real-world value</t>
+          <t>Your hash</t>
         </is>
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>points hors chaîne du prototype, sans valeur réelle</t>
+          <t>Ta puissance</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>你的算力</t>
+          <t>挖到的聪</t>
         </is>
       </c>
       <c r="B244" s="8" t="inlineStr">
         <is>
-          <t>你的算力</t>
+          <t>挖到的聪</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Your hash</t>
+          <t>Sats mined</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Ta puissance</t>
+          <t>Sats minés</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>挖到的聪</t>
+          <t>全网算力</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>挖到的聪</t>
+          <t>全网算力</t>
         </is>
       </c>
       <c r="C245" s="8" t="inlineStr">
         <is>
-          <t>Sats mined</t>
+          <t>Network hash</t>
         </is>
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>Sats minés</t>
+          <t>Puissance réseau</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>全网算力</t>
+          <t>已挖到</t>
         </is>
       </c>
       <c r="B246" s="8" t="inlineStr">
         <is>
-          <t>全网算力</t>
+          <t>已挖到</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>Network hash</t>
+          <t>Won</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Puissance réseau</t>
+          <t>Gagnés</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>已挖到</t>
+          <t>下个区块</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>已挖到</t>
+          <t>下个区块</t>
         </is>
       </c>
       <c r="C247" s="8" t="inlineStr">
         <is>
-          <t>Won</t>
+          <t>Next block</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>Gagnés</t>
+          <t>Prochain bloc</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>下个区块</t>
+          <t>剩余生命</t>
         </is>
       </c>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t>下个区块</t>
+          <t>剩余生命</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>Next block</t>
+          <t>Lives left</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Prochain bloc</t>
+          <t>Vies restantes</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>剩余生命</t>
+          <t>快捷键 Q / W / E 升级，X 回收</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>剩余生命</t>
+          <t>快捷键 Q / W / E 升级，X 回收</t>
         </is>
       </c>
       <c r="C249" s="8" t="inlineStr">
         <is>
-          <t>Lives left</t>
+          <t>Keys Q / W / E upgrade, X recycles</t>
         </is>
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>Vies restantes</t>
+          <t>Touches Q / W / E améliorer, X recycler</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>快捷键 Q / W / E 升级，X 回收</t>
+          <t>整数溢出！</t>
         </is>
       </c>
       <c r="B250" s="8" t="inlineStr">
         <is>
-          <t>快捷键 Q / W / E 升级，X 回收</t>
+          <t>整数溢出！</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Keys Q / W / E upgrade, X recycles</t>
+          <t>Integer overflow!</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Touches Q / W / E améliorer, X recycler</t>
+          <t>Dépassement d’entier !</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>整数溢出！</t>
+          <t>第一章</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>整数溢出！</t>
+          <t>第一章</t>
         </is>
       </c>
       <c r="C251" s="8" t="inlineStr">
         <is>
-          <t>Integer overflow!</t>
+          <t>Chapter 1</t>
         </is>
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>Dépassement d’entier !</t>
+          <t>Chapitre 1</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>第一章</t>
+          <t>通关「{x}」解锁</t>
         </is>
       </c>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>第一章</t>
+          <t>通关「{x}」解锁</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Chapter 1</t>
+          <t>Clear “{x}” to unlock</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Chapitre 1</t>
+          <t>Termine « {x} » pour débloquer</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>通关「{x}」解锁</t>
+          <t>挂上：{x}</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>通关「{x}」解锁</t>
+          <t>挂上：{x}</t>
         </is>
       </c>
       <c r="C253" s="8" t="inlineStr">
         <is>
-          <t>Clear “{x}” to unlock</t>
+          <t>Applies: {x}</t>
         </is>
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>Termine « {x} » pour débloquer</t>
+          <t>Applique : {x}</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>挂上：{x}</t>
+          <t>难度调整：全网算力 +{n}%</t>
         </is>
       </c>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>挂上：{x}</t>
+          <t>难度调整：全网算力 +{n}%</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Applies: {x}</t>
+          <t>Difficulty adjustment: network hash +{n}%</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Applique : {x}</t>
+          <t>Ajustement de difficulté : puissance réseau +{n} %</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>难度调整：全网算力 +{n}%</t>
+          <t>新知识卡</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>难度调整：全网算力 +{n}%</t>
+          <t>新知识卡</t>
         </is>
       </c>
       <c r="C255" s="8" t="inlineStr">
         <is>
-          <t>Difficulty adjustment: network hash +{n}%</t>
+          <t>New knowledge card</t>
         </is>
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>Ajustement de difficulté : puissance réseau +{n} %</t>
+          <t>Nouvelle carte savoir</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>新知识卡</t>
+          <t>⛏ 挖矿</t>
         </is>
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t>新知识卡</t>
+          <t>⛏ 挖矿</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>New knowledge card</t>
+          <t>⛏ Mining</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>Nouvelle carte savoir</t>
+          <t>⛏ Minage</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>⛏ 挖矿</t>
+          <t>获得积分</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>⛏ 挖矿</t>
+          <t>获得积分</t>
         </is>
       </c>
       <c r="C257" s="8" t="inlineStr">
         <is>
-          <t>⛏ Mining</t>
+          <t>Points earned</t>
         </is>
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>⛏ Minage</t>
+          <t>Points gagnés</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>获得积分</t>
+          <t>再点一次离开（本局进度不保存）</t>
         </is>
       </c>
       <c r="B258" s="8" t="inlineStr">
         <is>
-          <t>获得积分</t>
+          <t>再点一次离开（本局进度不保存）</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>Points earned</t>
+          <t>Tap again to leave (this run is not saved)</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>Points gagnés</t>
+          <t>Touche encore pour quitter (partie non sauvegardée)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>再点一次离开（本局进度不保存）</t>
+          <t>皮厚</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>再点一次离开（本局进度不保存）</t>
+          <t>皮厚</t>
         </is>
       </c>
       <c r="C259" s="8" t="inlineStr">
         <is>
-          <t>Tap again to leave (this run is not saved)</t>
+          <t>Tough</t>
         </is>
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>Touche encore pour quitter (partie non sauvegardée)</t>
+          <t>Coriace</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>皮厚</t>
+          <t>防水</t>
         </is>
       </c>
       <c r="B260" s="8" t="inlineStr">
         <is>
-          <t>皮厚</t>
+          <t>防水</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Tough</t>
+          <t>Waterproof</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>Coriace</t>
+          <t>Imperméable</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>防水</t>
+          <t>跳过！</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>防水</t>
+          <t>跳过！</t>
         </is>
       </c>
       <c r="C261" s="8" t="inlineStr">
         <is>
-          <t>Waterproof</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Imperméable</t>
+          <t>Hop !</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>跳过！</t>
+          <t>跑者</t>
         </is>
       </c>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t>跳过！</t>
+          <t>跑者</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Runners</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Hop !</t>
+          <t>Coureurs</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>跑者</t>
+          <t>对策</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>跑者</t>
+          <t>对策</t>
         </is>
       </c>
       <c r="C263" s="8" t="inlineStr">
         <is>
-          <t>Runners</t>
+          <t>Counter</t>
         </is>
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Coureurs</t>
+          <t>Parade</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>对策</t>
+          <t>还没遇到过。</t>
         </is>
       </c>
       <c r="B264" s="8" t="inlineStr">
         <is>
-          <t>对策</t>
+          <t>还没遇到过。</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Counter</t>
+          <t>Not met yet.</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Parade</t>
+          <t>Pas encore croisé.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>还没遇到过。</t>
+          <t>新跑者</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>还没遇到过。</t>
+          <t>新跑者</t>
         </is>
       </c>
       <c r="C265" s="8" t="inlineStr">
         <is>
-          <t>Not met yet.</t>
+          <t>New runner</t>
         </is>
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Pas encore croisé.</t>
+          <t>Nouveau coureur</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>新跑者</t>
+          <t>对{x}无效</t>
         </is>
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>新跑者</t>
+          <t>对{x}无效</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>New runner</t>
+          <t>No effect on {x}</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>Nouveau coureur</t>
+          <t>Sans effet sur {x}</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>对{x}无效</t>
+          <t>连撞 ×{n}</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>对{x}无效</t>
+          <t>连撞 ×{n}</t>
         </is>
       </c>
       <c r="C267" s="8" t="inlineStr">
         <is>
-          <t>No effect on {x}</t>
+          <t>Crash ×{n}</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Sans effet sur {x}</t>
+          <t>Collision ×{n}</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>连撞 ×{n}</t>
+          <t>整道铺皮！</t>
         </is>
       </c>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t>连撞 ×{n}</t>
+          <t>整道铺皮！</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>Crash ×{n}</t>
+          <t>Paved with peels!</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Collision ×{n}</t>
+          <t>Piste couverte !</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>整道铺皮！</t>
+          <t>后勤补给！</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>整道铺皮！</t>
+          <t>后勤补给！</t>
         </is>
       </c>
       <c r="C269" s="8" t="inlineStr">
         <is>
-          <t>Paved with peels!</t>
+          <t>Supplies in!</t>
         </is>
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Piste couverte !</t>
+          <t>Ravitaillement !</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>后勤补给！</t>
+          <t>重低音 ×{n}</t>
         </is>
       </c>
       <c r="B270" s="8" t="inlineStr">
         <is>
-          <t>后勤补给！</t>
+          <t>重低音 ×{n}</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>Supplies in!</t>
+          <t>Bass drop ×{n}</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Ravitaillement !</t>
+          <t>Basse ×{n}</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>重低音 ×{n}</t>
+          <t>限量发售！</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>重低音 ×{n}</t>
+          <t>限量发售！</t>
         </is>
       </c>
       <c r="C271" s="8" t="inlineStr">
         <is>
-          <t>Bass drop ×{n}</t>
+          <t>Launch event!</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Basse ×{n}</t>
+          <t>Lancement !</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>限量发售！</t>
+          <t>投递区已设定</t>
         </is>
       </c>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t>限量发售！</t>
+          <t>投递区已设定</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Launch event!</t>
+          <t>Drop zone set</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Lancement !</t>
+          <t>Zone de largage fixée</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>投递区已设定</t>
+          <t>布阵路段已设定</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>投递区已设定</t>
+          <t>布阵路段已设定</t>
         </is>
       </c>
       <c r="C273" s="8" t="inlineStr">
         <is>
-          <t>Drop zone set</t>
+          <t>Trap stretch set</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Zone de largage fixée</t>
+          <t>Tronçon piégé fixé</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>布阵路段已设定</t>
+          <t>副路线最多 2 级</t>
         </is>
       </c>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>布阵路段已设定</t>
+          <t>副路线最多 2 级</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Trap stretch set</t>
+          <t>Secondary path max tier 2</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Tronçon piégé fixé</t>
+          <t>Voie secondaire : niveau 2 max</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>副路线最多 2 级</t>
+          <t>6 级专精 −30%</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>副路线最多 2 级</t>
+          <t>6 级专精 −30%</t>
         </is>
       </c>
       <c r="C275" s="8" t="inlineStr">
         <is>
-          <t>Secondary path max tier 2</t>
+          <t>Tier-6 specialisation −30%</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Voie secondaire : niveau 2 max</t>
+          <t>Spécialisation niv. 6 −30 %</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>6 级专精 −30%</t>
+          <t>副</t>
         </is>
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>6 级专精 −30%</t>
+          <t>副</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Tier-6 specialisation −30%</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Spécialisation niv. 6 −30 %</t>
+          <t>2e</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>副</t>
+          <t>副路线</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>副</t>
+          <t>副路线</t>
         </is>
       </c>
       <c r="C277" s="8" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>Secondaire</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>副路线</t>
+          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
         </is>
       </c>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t>副路线</t>
+          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Tier 6 removes the secondary path; the {n} GST spent on it is credited</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Secondaire</t>
+          <t>Le niveau 6 retire la voie secondaire ; les {n} GST dépensés sont déduits</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
+          <t>点地图上的跑道…</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
+          <t>点地图上的跑道…</t>
         </is>
       </c>
       <c r="C279" s="8" t="inlineStr">
         <is>
-          <t>Tier 6 removes the secondary path; the {n} GST spent on it is credited</t>
+          <t>Tap the track…</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Le niveau 6 retire la voie secondaire ; les {n} GST dépensés sont déduits</t>
+          <t>Touche la piste…</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>点地图上的跑道…</t>
+          <t>🎯 设定投递区</t>
         </is>
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>点地图上的跑道…</t>
+          <t>🎯 设定投递区</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>Tap the track…</t>
+          <t>🎯 Set drop zone</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste…</t>
+          <t>🎯 Zone de largage</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>🎯 设定投递区</t>
+          <t>🎯 设定布阵路段</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>🎯 设定投递区</t>
+          <t>🎯 设定布阵路段</t>
         </is>
       </c>
       <c r="C281" s="8" t="inlineStr">
         <is>
-          <t>🎯 Set drop zone</t>
+          <t>🎯 Set trap stretch</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>🎯 Zone de largage</t>
+          <t>🎯 Tronçon à piéger</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>🎯 设定布阵路段</t>
+          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
         </is>
       </c>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t>🎯 设定布阵路段</t>
+          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>🎯 Set trap stretch</t>
+          <t>Two paths can each reach tier 2; the first to tier 3 becomes main (up to 5); tier 6 specialisation removes the secondary</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>🎯 Tronçon à piéger</t>
+          <t>Deux voies peuvent atteindre le niveau 2 ; la première au niveau 3 devient principale (jusqu’à 5) ; la spécialisation niv. 6 retire la secondaire</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
+          <t>{x} 专精！</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
+          <t>{x} 专精！</t>
         </is>
       </c>
       <c r="C283" s="8" t="inlineStr">
         <is>
-          <t>Two paths can each reach tier 2; the first to tier 3 becomes main (up to 5); tier 6 specialisation removes the secondary</t>
+          <t>{x} specialisation!</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Deux voies peuvent atteindre le niveau 2 ; la première au niveau 3 devient principale (jusqu’à 5) ; la spécialisation niv. 6 retire la secondaire</t>
+          <t>Spécialisation : {x} !</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>{x} 专精！</t>
+          <t>场上上限</t>
         </is>
       </c>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t>{x} 专精！</t>
+          <t>场上上限</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>{x} specialisation!</t>
+          <t>Max on track</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Spécialisation : {x} !</t>
+          <t>Max sur piste</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>场上上限</t>
+          <t>每次箱数</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>场上上限</t>
+          <t>每次箱数</t>
         </is>
       </c>
       <c r="C285" s="8" t="inlineStr">
         <is>
-          <t>Max on track</t>
+          <t>Boxes per run</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Max sur piste</t>
+          <t>Boîtes par sortie</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>每次箱数</t>
+          <t>每次招呼</t>
         </is>
       </c>
       <c r="B286" s="8" t="inlineStr">
         <is>
-          <t>每次箱数</t>
+          <t>每次招呼</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>Boxes per run</t>
+          <t>Per invite</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Boîtes par sortie</t>
+          <t>Par invitation</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>每次招呼</t>
+          <t>停留</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>每次招呼</t>
+          <t>停留</t>
         </is>
       </c>
       <c r="C287" s="8" t="inlineStr">
         <is>
-          <t>Per invite</t>
+          <t>Stay</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Par invitation</t>
+          <t>Arrêt</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>停留</t>
+          <t>{x} 的动画 JSON 读不出来</t>
         </is>
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>停留</t>
+          <t>{x} 的动画 JSON 读不出来</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Could not read the animation JSON for {x}</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Arrêt</t>
+          <t>Impossible de lire le JSON d’animation de {x}</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>{x} 的动画 JSON 读不出来</t>
+          <t>弹道 {x} {k}</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>{x} 的动画 JSON 读不出来</t>
+          <t>弹道 {x} {k}</t>
         </is>
       </c>
       <c r="C289" s="8" t="inlineStr">
         <is>
-          <t>Could not read the animation JSON for {x}</t>
+          <t>Trajectory {x} {k}</t>
         </is>
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Impossible de lire le JSON d’animation de {x}</t>
+          <t>Trajectoire {x} {k}</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>弹道 {x} {k}</t>
+          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
         </is>
       </c>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>弹道 {x} {k}</t>
+          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Trajectory {x} {k}</t>
+          <t>Device {x}: base extra effect “{y}” is malformed, kept the original</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Trajectoire {x} {k}</t>
+          <t>Dispositif {x} : effet de base « {y} » mal écrit, original conservé</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
+          <t>导入美术图片 / 动画（可多选）</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
+          <t>导入美术图片 / 动画（可多选）</t>
         </is>
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
-          <t>Device {x}: base extra effect “{y}” is malformed, kept the original</t>
+          <t>Import art / animations (multi-select)</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Dispositif {x} : effet de base « {y} » mal écrit, original conservé</t>
+          <t>Importer images / animations (plusieurs)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>导入美术图片 / 动画（可多选）</t>
+          <t>点跑道，设定投递区（Esc 取消）</t>
         </is>
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>导入美术图片 / 动画（可多选）</t>
+          <t>点跑道，设定投递区（Esc 取消）</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Import art / animations (multi-select)</t>
+          <t>Tap the track to set the drop zone (Esc to cancel)</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Importer images / animations (plusieurs)</t>
+          <t>Touche la piste pour choisir la zone de largage (Échap pour annuler)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>点跑道，设定投递区（Esc 取消）</t>
+          <t>点跑道，设定布阵路段（Esc 取消）</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>点跑道，设定投递区（Esc 取消）</t>
+          <t>点跑道，设定布阵路段（Esc 取消）</t>
         </is>
       </c>
       <c r="C293" s="8" t="inlineStr">
         <is>
-          <t>Tap the track to set the drop zone (Esc to cancel)</t>
+          <t>Tap the track to set the trap stretch (Esc to cancel)</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste pour choisir la zone de largage (Échap pour annuler)</t>
+          <t>Touche la piste pour choisir le tronçon à piéger (Échap pour annuler)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>点跑道，设定布阵路段（Esc 取消）</t>
+          <t>放不下</t>
         </is>
       </c>
       <c r="B294" s="8" t="inlineStr">
         <is>
-          <t>点跑道，设定布阵路段（Esc 取消）</t>
+          <t>放不下</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Tap the track to set the trap stretch (Esc to cancel)</t>
+          <t>No room</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste pour choisir le tronçon à piéger (Échap pour annuler)</t>
+          <t>Pas de place</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>放不下</t>
+          <t>再点一次重新开始</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>放不下</t>
+          <t>再点一次重新开始</t>
         </is>
       </c>
       <c r="C295" s="8" t="inlineStr">
         <is>
-          <t>No room</t>
+          <t>Tap again to restart</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Pas de place</t>
+          <t>Touche encore pour recommencer</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>再点一次重新开始</t>
+          <t>重开本关</t>
         </is>
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>再点一次重新开始</t>
+          <t>重开本关</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Tap again to restart</t>
+          <t>Restart level</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Touche encore pour recommencer</t>
+          <t>Rejouer le niveau</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>重开本关</t>
+          <t>重新开始</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>重开本关</t>
+          <t>重新开始</t>
         </is>
       </c>
       <c r="C297" s="8" t="inlineStr">
         <is>
-          <t>Restart level</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Rejouer le niveau</t>
+          <t>Recommencer</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>重新开始</t>
+          <t>↻ 重新开始</t>
         </is>
       </c>
       <c r="B298" s="8" t="inlineStr">
         <is>
-          <t>重新开始</t>
+          <t>↻ 重新开始</t>
         </is>
       </c>
       <c r="C298" s="8" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>↻ Restart</t>
         </is>
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>Recommencer</t>
+          <t>↻ Recommencer</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>↻ 重新开始</t>
+          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>↻ 重新开始</t>
+          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
         </is>
       </c>
       <c r="C299" s="8" t="inlineStr">
         <is>
-          <t>↻ Restart</t>
+          <t>Tap any free ground off the track to place a device (each device takes a different number of cells), then tap it to upgrade. Each device can grow two paths: both can reach tier 2, the first to tier 3 becomes main and goes up to 5; tier 6 specialisation removes the secondary path and credits what you spent on it.</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>↻ Recommencer</t>
+          <t>Touche n’importe quel terrain libre hors de la piste pour poser un dispositif (chacun occupe un nombre de cases différent), puis touche-le pour l’améliorer. Deux voies maximum : les deux peuvent atteindre le niveau 2, la première au niveau 3 devient principale jusqu’au 5 ; la spécialisation niv. 6 retire la secondaire et déduit ce que tu y as dépensé.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
         </is>
       </c>
       <c r="B300" s="8" t="inlineStr">
         <is>
-          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
         </is>
       </c>
       <c r="C300" s="8" t="inlineStr">
         <is>
-          <t>Tap any free ground off the track to place a device (each device takes a different number of cells), then tap it to upgrade. Each device can grow two paths: both can reach tier 2, the first to tier 3 becomes main and goes up to 5; tier 6 specialisation removes the secondary path and credits what you spent on it.</t>
+          <t>Tap any free ground off the track to place a device, then tap the device to upgrade it.</t>
         </is>
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>Touche n’importe quel terrain libre hors de la piste pour poser un dispositif (chacun occupe un nombre de cases différent), puis touche-le pour l’améliorer. Deux voies maximum : les deux peuvent atteindre le niveau 2, la première au niveau 3 devient principale jusqu’au 5 ; la spécialisation niv. 6 retire la secondaire et déduit ce que tu y as dépensé.</t>
+          <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis touchez-le pour l’améliorer.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+          <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+          <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
         </is>
       </c>
       <c r="C301" s="8" t="inlineStr">
         <is>
-          <t>Tap any free ground off the track to place a device, then tap the device to upgrade it.</t>
+          <t>Tap free ground off the track to place a device, then press “Start wave 1”</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis touchez-le pour l’améliorer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="6" t="inlineStr">
-        <is>
-          <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
-        </is>
-      </c>
-      <c r="B302" s="8" t="inlineStr">
-        <is>
-          <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
-        </is>
-      </c>
-      <c r="C302" s="8" t="inlineStr">
-        <is>
-          <t>Tap free ground off the track to place a device, then press “Start wave 1”</t>
-        </is>
-      </c>
-      <c r="D302" s="8" t="inlineStr">
-        <is>
           <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis « Lancer la vague 1 »</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="10" t="inlineStr">
+    <row r="303">
+      <c r="A303" s="10" t="inlineStr">
         <is>
           <t>※ 花括号里的 {n}、{x} 等是占位符，翻译时要原样保留。</t>
         </is>
@@ -22084,7 +22115,7 @@
         <v>120</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="H41" s="14">
         <f>G41/F41*100</f>
@@ -22124,7 +22155,7 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>喷头加长</t>
+          <t>加长水管</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
@@ -22134,7 +22165,7 @@
         <v>180</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>2.73</v>
+        <v>3.31</v>
       </c>
       <c r="H42" s="14">
         <f>G42/F42*100</f>
@@ -22158,7 +22189,11 @@
         <f>IF(OR(K42="",L42="",L42=0),"",K42/L42)</f>
         <v/>
       </c>
-      <c r="N42" s="9" t="inlineStr"/>
+      <c r="N42" s="9" t="inlineStr">
+        <is>
+          <t>活动范围</t>
+        </is>
+      </c>
       <c r="O42" s="9">
         <f>IF(B42=0,"基准",IF(C42=6,"6 级专精：空位用完后的出路，看后期实测，不和多放基础塔比",IF(AND(N42&lt;&gt;"",I42&lt;0.85),"功能型：单看输出偏低属正常",IF(I42&gt;=0.85,"划算",IF(I42&gt;=0.65,"略亏：空位紧张时仍值得","偏亏：建议降价或加强")))))</f>
         <v/>
@@ -22188,7 +22223,7 @@
         <v>260</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>2.73</v>
+        <v>3.31</v>
       </c>
       <c r="H43" s="14">
         <f>G43/F43*100</f>
@@ -22246,7 +22281,7 @@
         <v>540</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>4.54</v>
+        <v>5.51</v>
       </c>
       <c r="H44" s="14">
         <f>G44/F44*100</f>
@@ -22300,7 +22335,7 @@
         <v>1140</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>6.49</v>
+        <v>7.87</v>
       </c>
       <c r="H45" s="14">
         <f>G45/F45*100</f>
@@ -22358,7 +22393,7 @@
         <v>2440</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>8.35</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H46" s="14">
         <f>G46/F46*100</f>
@@ -22466,7 +22501,7 @@
         <v>165</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="H48" s="14">
         <f>G48/F48*100</f>
@@ -22524,7 +22559,7 @@
         <v>245</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="H49" s="14">
         <f>G49/F49*100</f>
@@ -22582,7 +22617,7 @@
         <v>545</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="H50" s="14">
         <f>G50/F50*100</f>
@@ -22640,7 +22675,7 @@
         <v>1195</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="H51" s="14">
         <f>G51/F51*100</f>
@@ -22694,7 +22729,7 @@
         <v>2595</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="H52" s="14">
         <f>G52/F52*100</f>
@@ -22748,7 +22783,7 @@
         <v>5995</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>11.28</v>
+        <v>13.78</v>
       </c>
       <c r="H53" s="14">
         <f>G53/F53*100</f>
@@ -22802,7 +22837,7 @@
         <v>180</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="H54" s="14">
         <f>G54/F54*100</f>
@@ -22856,7 +22891,7 @@
         <v>290</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>5.76</v>
+        <v>6.77</v>
       </c>
       <c r="H55" s="14">
         <f>G55/F55*100</f>
@@ -22880,7 +22915,11 @@
         <f>IF(OR(K55="",L55="",L55=0),"",K55/L55)</f>
         <v/>
       </c>
-      <c r="N55" s="9" t="inlineStr"/>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t>车速</t>
+        </is>
+      </c>
       <c r="O55" s="9">
         <f>IF(B55=0,"基准",IF(C55=6,"6 级专精：空位用完后的出路，看后期实测，不和多放基础塔比",IF(AND(N55&lt;&gt;"",I55&lt;0.85),"功能型：单看输出偏低属正常",IF(I55&gt;=0.85,"划算",IF(I55&gt;=0.65,"略亏：空位紧张时仍值得","偏亏：建议降价或加强")))))</f>
         <v/>
@@ -22910,7 +22949,7 @@
         <v>590</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>5.76</v>
+        <v>6.77</v>
       </c>
       <c r="H56" s="14">
         <f>G56/F56*100</f>
@@ -22968,7 +23007,7 @@
         <v>1140</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>11.94</v>
+        <v>13.51</v>
       </c>
       <c r="H57" s="14">
         <f>G57/F57*100</f>
@@ -23022,7 +23061,7 @@
         <v>2540</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>23.89</v>
+        <v>27.02</v>
       </c>
       <c r="H58" s="14">
         <f>G58/F58*100</f>
@@ -23076,7 +23115,7 @@
         <v>5940</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>71.66</v>
+        <v>81.06</v>
       </c>
       <c r="H59" s="14">
         <f>G59/F59*100</f>
@@ -27185,47 +27224,47 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>洒水器</t>
+          <t>洒水车</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Sprinkler</t>
+          <t>Truck</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Arroseur</t>
+          <t>Camion</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>洒水器</t>
+          <t>洒水车</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Sprinkler</t>
+          <t>Truck</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Arroseur</t>
+          <t>Camion</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>持续喷水：范围内的跑者被淋湿、减速</t>
+          <t>会自己开的洒水车：在消防栓周围一圈里追着跑者开，喷到的跑者被淋湿、减速</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Keeps spraying: runners in range get wet and slowed</t>
+          <t>Drives itself around its hydrant, chasing runners; everyone it sprays gets wet and slowed</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Arrose en continu : les coureurs à portée sont mouillés et ralentis</t>
+          <t>Roule tout seul autour de sa borne à la poursuite des coureurs ; tous ceux qu’il arrose sont trempés et ralentis</t>
         </is>
       </c>
       <c r="K5" s="7" t="n">
@@ -27238,7 +27277,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="O5" s="7" t="n">
         <v>0</v>
@@ -27268,7 +27307,7 @@
       </c>
       <c r="W5" s="7" t="inlineStr">
         <is>
-          <t>frostNeed=4; freezeCap=99</t>
+          <t>frostNeed=4; freezeCap=99; patrol=60; drive=65</t>
         </is>
       </c>
       <c r="X5" s="7" t="n">
@@ -30407,17 +30446,17 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>喷头加长</t>
+          <t>加长水管</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Longer Reach</t>
+          <t>Longer Hose</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Portée accrue</t>
+          <t>Tuyau rallongé</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
@@ -30425,22 +30464,22 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>射程 +15</t>
+          <t>活动范围 +25，射程 +5</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Range +15</t>
+          <t>Patrol +25, range +5</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>Portée +15</t>
+          <t>Patrouille +25, portée +5</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>range+=15</t>
+          <t>patrol+=25; range+=5</t>
         </is>
       </c>
       <c r="L39" s="9">
@@ -31140,22 +31179,22 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>效果 +0.5</t>
+          <t>效果 +0.5，车速 +30%</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Effect +0.5</t>
+          <t>Effect +0.5, drives 30% faster</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Effet +0,5</t>
+          <t>Effet +0,5, roule 30 % plus vite</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>dmg+=0.5</t>
+          <t>dmg+=0.5; drive*=1.3</t>
         </is>
       </c>
       <c r="L52" s="9">

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -12470,7 +12470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D308"/>
+  <dimension ref="A1:D309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -18444,775 +18444,797 @@
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>连撞 ×{n}</t>
+          <t>闪避</t>
         </is>
       </c>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t>连撞 ×{n}</t>
+          <t>闪避</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Crash ×{n}</t>
+          <t>Dodge</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Collision ×{n}</t>
+          <t>Esquive</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>整道铺皮！</t>
+          <t>连撞 ×{n}</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>整道铺皮！</t>
+          <t>连撞 ×{n}</t>
         </is>
       </c>
       <c r="C273" s="8" t="inlineStr">
         <is>
-          <t>Paved with peels!</t>
+          <t>Crash ×{n}</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Piste couverte !</t>
+          <t>Collision ×{n}</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>后勤补给！</t>
+          <t>整道铺皮！</t>
         </is>
       </c>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>后勤补给！</t>
+          <t>整道铺皮！</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Supplies in!</t>
+          <t>Paved with peels!</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Ravitaillement !</t>
+          <t>Piste couverte !</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>重低音 ×{n}</t>
+          <t>后勤补给！</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>重低音 ×{n}</t>
+          <t>后勤补给！</t>
         </is>
       </c>
       <c r="C275" s="8" t="inlineStr">
         <is>
-          <t>Bass drop ×{n}</t>
+          <t>Supplies in!</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Basse ×{n}</t>
+          <t>Ravitaillement !</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>限量发售！</t>
+          <t>重低音 ×{n}</t>
         </is>
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>限量发售！</t>
+          <t>重低音 ×{n}</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Launch event!</t>
+          <t>Bass drop ×{n}</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Lancement !</t>
+          <t>Basse ×{n}</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>投递区已设定</t>
+          <t>限量发售！</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>投递区已设定</t>
+          <t>限量发售！</t>
         </is>
       </c>
       <c r="C277" s="8" t="inlineStr">
         <is>
-          <t>Drop zone set</t>
+          <t>Launch event!</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Zone de largage fixée</t>
+          <t>Lancement !</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>布阵路段已设定</t>
+          <t>投递区已设定</t>
         </is>
       </c>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t>布阵路段已设定</t>
+          <t>投递区已设定</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Trap stretch set</t>
+          <t>Drop zone set</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Tronçon piégé fixé</t>
+          <t>Zone de largage fixée</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>副路线最多 2 级</t>
+          <t>布阵路段已设定</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>副路线最多 2 级</t>
+          <t>布阵路段已设定</t>
         </is>
       </c>
       <c r="C279" s="8" t="inlineStr">
         <is>
-          <t>Secondary path max tier 2</t>
+          <t>Trap stretch set</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Voie secondaire : niveau 2 max</t>
+          <t>Tronçon piégé fixé</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>6 级专精 −30%</t>
+          <t>副路线最多 2 级</t>
         </is>
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>6 级专精 −30%</t>
+          <t>副路线最多 2 级</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>Tier-6 specialisation −30%</t>
+          <t>Secondary path max tier 2</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Spécialisation niv. 6 −30 %</t>
+          <t>Voie secondaire : niveau 2 max</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>副</t>
+          <t>6 级专精 −30%</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>副</t>
+          <t>6 级专精 −30%</t>
         </is>
       </c>
       <c r="C281" s="8" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Tier-6 specialisation −30%</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>Spécialisation niv. 6 −30 %</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>副路线</t>
+          <t>副</t>
         </is>
       </c>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t>副路线</t>
+          <t>副</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Secondaire</t>
+          <t>2e</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
+          <t>副路线</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
+          <t>副路线</t>
         </is>
       </c>
       <c r="C283" s="8" t="inlineStr">
         <is>
-          <t>Tier 6 removes the secondary path; the {n} GST spent on it is credited</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Le niveau 6 retire la voie secondaire ; les {n} GST dépensés sont déduits</t>
+          <t>Secondaire</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>点地图上的跑道…</t>
+          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
         </is>
       </c>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t>点地图上的跑道…</t>
+          <t>6 级会移除副路线，已花的 {n} GST 抵扣</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>Tap the track…</t>
+          <t>Tier 6 removes the secondary path; the {n} GST spent on it is credited</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste…</t>
+          <t>Le niveau 6 retire la voie secondaire ; les {n} GST dépensés sont déduits</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>🎯 设定投递区</t>
+          <t>点地图上的跑道…</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>🎯 设定投递区</t>
+          <t>点地图上的跑道…</t>
         </is>
       </c>
       <c r="C285" s="8" t="inlineStr">
         <is>
-          <t>🎯 Set drop zone</t>
+          <t>Tap the track…</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>🎯 Zone de largage</t>
+          <t>Touche la piste…</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>🎯 设定布阵路段</t>
+          <t>🎯 设定投递区</t>
         </is>
       </c>
       <c r="B286" s="8" t="inlineStr">
         <is>
-          <t>🎯 设定布阵路段</t>
+          <t>🎯 设定投递区</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>🎯 Set trap stretch</t>
+          <t>🎯 Set drop zone</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>🎯 Tronçon à piéger</t>
+          <t>🎯 Zone de largage</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
+          <t>🎯 设定布阵路段</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
+          <t>🎯 设定布阵路段</t>
         </is>
       </c>
       <c r="C287" s="8" t="inlineStr">
         <is>
-          <t>Two paths can each reach tier 2; the first to tier 3 becomes main (up to 5); tier 6 specialisation removes the secondary</t>
+          <t>🎯 Set trap stretch</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Deux voies peuvent atteindre le niveau 2 ; la première au niveau 3 devient principale (jusqu’à 5) ; la spécialisation niv. 6 retire la secondaire</t>
+          <t>🎯 Tronçon à piéger</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>{x} 专精！</t>
+          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
         </is>
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>{x} 专精！</t>
+          <t>两条路线可各升到 2 级；先到 3 级的是主路线，最高 5 级；6 级专精会移除副路线</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>{x} specialisation!</t>
+          <t>Two paths can each reach tier 2; the first to tier 3 becomes main (up to 5); tier 6 specialisation removes the secondary</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Spécialisation : {x} !</t>
+          <t>Deux voies peuvent atteindre le niveau 2 ; la première au niveau 3 devient principale (jusqu’à 5) ; la spécialisation niv. 6 retire la secondaire</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>场上上限</t>
+          <t>{x} 专精！</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>场上上限</t>
+          <t>{x} 专精！</t>
         </is>
       </c>
       <c r="C289" s="8" t="inlineStr">
         <is>
-          <t>Max on track</t>
+          <t>{x} specialisation!</t>
         </is>
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Max sur piste</t>
+          <t>Spécialisation : {x} !</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>每次箱数</t>
+          <t>场上上限</t>
         </is>
       </c>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>每次箱数</t>
+          <t>场上上限</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Boxes per run</t>
+          <t>Max on track</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Boîtes par sortie</t>
+          <t>Max sur piste</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>每次招呼</t>
+          <t>每次箱数</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>每次招呼</t>
+          <t>每次箱数</t>
         </is>
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
-          <t>Per invite</t>
+          <t>Boxes per run</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Par invitation</t>
+          <t>Boîtes par sortie</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>停留</t>
+          <t>每次招呼</t>
         </is>
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>停留</t>
+          <t>每次招呼</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Per invite</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Arrêt</t>
+          <t>Par invitation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>{x} 的动画 JSON 读不出来</t>
+          <t>停留</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>{x} 的动画 JSON 读不出来</t>
+          <t>停留</t>
         </is>
       </c>
       <c r="C293" s="8" t="inlineStr">
         <is>
-          <t>Could not read the animation JSON for {x}</t>
+          <t>Stay</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Impossible de lire le JSON d’animation de {x}</t>
+          <t>Arrêt</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>弹道 {x} {k}</t>
+          <t>{x} 的动画 JSON 读不出来</t>
         </is>
       </c>
       <c r="B294" s="8" t="inlineStr">
         <is>
-          <t>弹道 {x} {k}</t>
+          <t>{x} 的动画 JSON 读不出来</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Trajectory {x} {k}</t>
+          <t>Could not read the animation JSON for {x}</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Trajectoire {x} {k}</t>
+          <t>Impossible de lire le JSON d’animation de {x}</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
+          <t>弹道 {x} {k}</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
+          <t>弹道 {x} {k}</t>
         </is>
       </c>
       <c r="C295" s="8" t="inlineStr">
         <is>
-          <t>Device {x}: base extra effect “{y}” is malformed, kept the original</t>
+          <t>Trajectory {x} {k}</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Dispositif {x} : effet de base « {y} » mal écrit, original conservé</t>
+          <t>Trajectoire {x} {k}</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>导入美术图片 / 动画（可多选）</t>
+          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
         </is>
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>导入美术图片 / 动画（可多选）</t>
+          <t>装置 {x}：基础附加效果「{y}」写法有误，保留原效果</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Import art / animations (multi-select)</t>
+          <t>Device {x}: base extra effect “{y}” is malformed, kept the original</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Importer images / animations (plusieurs)</t>
+          <t>Dispositif {x} : effet de base « {y} » mal écrit, original conservé</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>点跑道，设定投递区（Esc 取消）</t>
+          <t>导入美术图片 / 动画（可多选）</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>点跑道，设定投递区（Esc 取消）</t>
+          <t>导入美术图片 / 动画（可多选）</t>
         </is>
       </c>
       <c r="C297" s="8" t="inlineStr">
         <is>
-          <t>Tap the track to set the drop zone (Esc to cancel)</t>
+          <t>Import art / animations (multi-select)</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste pour choisir la zone de largage (Échap pour annuler)</t>
+          <t>Importer images / animations (plusieurs)</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>点跑道，设定布阵路段（Esc 取消）</t>
+          <t>点跑道，设定投递区（Esc 取消）</t>
         </is>
       </c>
       <c r="B298" s="8" t="inlineStr">
         <is>
-          <t>点跑道，设定布阵路段（Esc 取消）</t>
+          <t>点跑道，设定投递区（Esc 取消）</t>
         </is>
       </c>
       <c r="C298" s="8" t="inlineStr">
         <is>
-          <t>Tap the track to set the trap stretch (Esc to cancel)</t>
+          <t>Tap the track to set the drop zone (Esc to cancel)</t>
         </is>
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>Touche la piste pour choisir le tronçon à piéger (Échap pour annuler)</t>
+          <t>Touche la piste pour choisir la zone de largage (Échap pour annuler)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>放不下</t>
+          <t>点跑道，设定布阵路段（Esc 取消）</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>放不下</t>
+          <t>点跑道，设定布阵路段（Esc 取消）</t>
         </is>
       </c>
       <c r="C299" s="8" t="inlineStr">
         <is>
-          <t>No room</t>
+          <t>Tap the track to set the trap stretch (Esc to cancel)</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Pas de place</t>
+          <t>Touche la piste pour choisir le tronçon à piéger (Échap pour annuler)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>再点一次重新开始</t>
+          <t>放不下</t>
         </is>
       </c>
       <c r="B300" s="8" t="inlineStr">
         <is>
-          <t>再点一次重新开始</t>
+          <t>放不下</t>
         </is>
       </c>
       <c r="C300" s="8" t="inlineStr">
         <is>
-          <t>Tap again to restart</t>
+          <t>No room</t>
         </is>
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>Touche encore pour recommencer</t>
+          <t>Pas de place</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>重开本关</t>
+          <t>再点一次重新开始</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>重开本关</t>
+          <t>再点一次重新开始</t>
         </is>
       </c>
       <c r="C301" s="8" t="inlineStr">
         <is>
-          <t>Restart level</t>
+          <t>Tap again to restart</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Rejouer le niveau</t>
+          <t>Touche encore pour recommencer</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>重新开始</t>
+          <t>重开本关</t>
         </is>
       </c>
       <c r="B302" s="8" t="inlineStr">
         <is>
-          <t>重新开始</t>
+          <t>重开本关</t>
         </is>
       </c>
       <c r="C302" s="8" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Restart level</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>Recommencer</t>
+          <t>Rejouer le niveau</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>↻ 重新开始</t>
+          <t>重新开始</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>↻ 重新开始</t>
+          <t>重新开始</t>
         </is>
       </c>
       <c r="C303" s="8" t="inlineStr">
         <is>
-          <t>↻ Restart</t>
+          <t>Restart</t>
         </is>
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>↻ Recommencer</t>
+          <t>Recommencer</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+          <t>↻ 重新开始</t>
         </is>
       </c>
       <c r="B304" s="8" t="inlineStr">
         <is>
-          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
+          <t>↻ 重新开始</t>
         </is>
       </c>
       <c r="C304" s="8" t="inlineStr">
         <is>
-          <t>Tap any free ground off the track to place a device (each device takes a different number of cells), then tap it to upgrade. Each device can grow two paths: both can reach tier 2, the first to tier 3 becomes main and goes up to 5; tier 6 specialisation removes the secondary path and credits what you spent on it.</t>
+          <t>↻ Restart</t>
         </is>
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>Touche n’importe quel terrain libre hors de la piste pour poser un dispositif (chacun occupe un nombre de cases différent), puis touche-le pour l’améliorer. Deux voies maximum : les deux peuvent atteindre le niveau 2, la première au niveau 3 devient principale jusqu’au 5 ; la spécialisation niv. 6 retire la secondaire et déduit ce que tu y as dépensé.</t>
+          <t>↻ Recommencer</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+          <t>点跑道外任意空地放置装置（每种装置占的格子不同），再点已放的装置升级。每个装置最多发展两条路线：都能先升到 2 级，先到 3 级的成为主路线，可升到 5 级；6 级专精会移除副路线，已花的钱抵扣。</t>
         </is>
       </c>
       <c r="C305" s="8" t="inlineStr">
         <is>
-          <t>Tap any free ground off the track to place a device, then tap the device to upgrade it.</t>
+          <t>Tap any free ground off the track to place a device (each device takes a different number of cells), then tap it to upgrade. Each device can grow two paths: both can reach tier 2, the first to tier 3 becomes main and goes up to 5; tier 6 specialisation removes the secondary path and credits what you spent on it.</t>
         </is>
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis touchez-le pour l’améliorer.</t>
+          <t>Touche n’importe quel terrain libre hors de la piste pour poser un dispositif (chacun occupe un nombre de cases différent), puis touche-le pour l’améliorer. Deux voies maximum : les deux peuvent atteindre le niveau 2, la première au niveau 3 devient principale jusqu’au 5 ; la spécialisation niv. 6 retire la secondaire et déduit ce que tu y as dépensé.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
+          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+        </is>
+      </c>
+      <c r="B306" s="8" t="inlineStr">
+        <is>
+          <t>点跑道外的空地放置装置，再点装置直接升级。</t>
+        </is>
+      </c>
+      <c r="C306" s="8" t="inlineStr">
+        <is>
+          <t>Tap any free ground off the track to place a device, then tap the device to upgrade it.</t>
+        </is>
+      </c>
+      <c r="D306" s="8" t="inlineStr">
+        <is>
+          <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis touchez-le pour l’améliorer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="6" t="inlineStr">
+        <is>
           <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
         </is>
       </c>
-      <c r="B306" s="8" t="inlineStr">
+      <c r="B307" s="8" t="inlineStr">
         <is>
           <t>点跑道外的空地放置装置，再点「开始第 1 波」</t>
         </is>
       </c>
-      <c r="C306" s="8" t="inlineStr">
+      <c r="C307" s="8" t="inlineStr">
         <is>
           <t>Tap free ground off the track to place a device, then press “Start wave 1”</t>
         </is>
       </c>
-      <c r="D306" s="8" t="inlineStr">
+      <c r="D307" s="8" t="inlineStr">
         <is>
           <t>Touchez un terrain libre hors de la piste pour poser un dispositif, puis « Lancer la vague 1 »</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="10" t="inlineStr">
+    <row r="309">
+      <c r="A309" s="10" t="inlineStr">
         <is>
           <t>※ 花括号里的 {n}、{x} 等是占位符，翻译时要原样保留。</t>
         </is>
@@ -27094,7 +27116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -28069,508 +28091,628 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>slowCap</t>
+          <t>bibWave</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.85</v>
+        <v>3</v>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>减速上限</t>
+          <t>号码布变体从第几波开始出现（之前全是标准白号码布）</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>bossSlowMult</t>
+          <t>bibLightPct</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Boss 受减速的比例（未升「冰桶挑战」时）</t>
+          <t>轻装号码布（绿号码布、脚下绿圈）出现概率</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>bossStunMult</t>
+          <t>bibRacePct</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Boss 受眩晕时长比例</t>
+          <t>竞速号码布（红号码布、脚下红圈）出现概率</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>miniHp</t>
+          <t>bibDodge</t>
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>跑团：跟跑者体力占原跑者比例</t>
+          <t>轻装号码布：躲开装置攻击的概率</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>miniGold</t>
+          <t>bibLightHp</t>
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>跟跑者 GST</t>
+          <t>轻装号码布：体力倍率</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>miniSpeed</t>
+          <t>bibRaceHp</t>
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>跟跑者速度倍率</t>
+          <t>竞速号码布：体力倍率</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>shieldPct</t>
+          <t>bibRaceSpd</t>
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.35</v>
+        <v>1.2</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>能量盾占体力比例</t>
+          <t>竞速号码布：速度倍率</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>regenPct</t>
+          <t>bibRaceCtl</t>
         </is>
       </c>
       <c r="B72" s="7" t="n">
-        <v>0.05</v>
+        <v>1.5</v>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>补给词缀：每秒回复比例</t>
+          <t>竞速号码布：受减速、诱惑站吸引的效果倍率（减速仍受减速上限限制）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>regenDelay</t>
+          <t>slowCap</t>
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>补给词缀：多久没被干扰开始回复（秒）</t>
+          <t>减速上限</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>swiftMult</t>
+          <t>bossSlowMult</t>
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>冲刺词缀：速度倍率</t>
+          <t>Boss 受减速的比例（未升「冰桶挑战」时）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>shrapnelRange</t>
+          <t>bossStunMult</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>90</v>
+        <v>0.25</v>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>香蕉碎片：溅射距离</t>
+          <t>Boss 受眩晕时长比例</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>shrapnelPct</t>
+          <t>miniHp</t>
         </is>
       </c>
       <c r="B76" s="7" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>香蕉碎片：每块效果比例</t>
+          <t>跑团：跟跑者体力占原跑者比例</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>clusterPct</t>
+          <t>miniGold</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>小香蕉：效果比例</t>
+          <t>跟跑者 GST</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>firePatchDps</t>
+          <t>miniSpeed</t>
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>辣油泼地：每秒效果比例</t>
+          <t>跟跑者速度倍率</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>infernoRadius</t>
+          <t>shieldPct</t>
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>42</v>
+        <v>0.35</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>火锅底料：溅射半径</t>
+          <t>能量盾占体力比例</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>iceAgeFreeze</t>
+          <t>regenPct</t>
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>人工降雪：冻结时长（秒）</t>
+          <t>补给词缀：每秒回复比例</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>ricochetPct</t>
+          <t>regenDelay</t>
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>弹跳鞋盒：效果比例</t>
+          <t>补给词缀：多久没被干扰开始回复（秒）</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>ricochetRange</t>
+          <t>swiftMult</t>
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>120</v>
+        <v>1.4</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>弹跳鞋盒：弹跳距离</t>
+          <t>冲刺词缀：速度倍率</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>decapBossPct</t>
+          <t>shrapnelRange</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>0.15</v>
+        <v>90</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>神秘箱轰炸：扣 Boss 最大体力比例</t>
+          <t>香蕉碎片：溅射距离</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>decapMult</t>
+          <t>shrapnelPct</t>
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>神秘箱轰炸：对非 Boss 倍率</t>
+          <t>香蕉碎片：每块效果比例</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>teslaHop</t>
+          <t>clusterPct</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>70</v>
+        <v>0.4</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>广场舞音响：传播距离</t>
+          <t>小香蕉：效果比例</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>blockTarget</t>
+          <t>firePatchDps</t>
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>16</v>
+        <v>0.6</v>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>挖矿：全网平均出块间隔（秒）</t>
+          <t>辣油泼地：每秒效果比例</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>blockReward</t>
+          <t>infernoRadius</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
-        <v>5000</v>
+        <v>42</v>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>挖矿：每个区块奖励的聪</t>
+          <t>火锅底料：溅射半径</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>adjustEvery</t>
+          <t>iceAgeFreeze</t>
         </is>
       </c>
       <c r="B88" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>挖矿：每多少个区块调整一次难度</t>
+          <t>人工降雪：冻结时长（秒）</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>netGrowth</t>
+          <t>ricochetPct</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>挖矿：每次难度调整全网算力上涨比例</t>
+          <t>弹跳鞋盒：效果比例</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>freeNet</t>
+          <t>ricochetRange</t>
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>挖矿：经典模式的全网初始算力</t>
+          <t>弹跳鞋盒：弹跳距离</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>rerollSats</t>
+          <t>decapBossPct</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
-        <v>1500</v>
+        <v>0.15</v>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>区块奖励重抽一次花费的聪</t>
+          <t>神秘箱轰炸：扣 Boss 最大体力比例</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>padTrackGap</t>
+          <t>decapMult</t>
         </is>
       </c>
       <c r="B92" s="7" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>额外放置点：离跑道中心线的最小距离</t>
+          <t>神秘箱轰炸：对非 Boss 倍率</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>padGap</t>
+          <t>teslaHop</t>
         </is>
       </c>
       <c r="B93" s="7" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>额外放置点：离其他空位的最小距离</t>
+          <t>广场舞音响：传播距离</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>gridTrackGap</t>
+          <t>blockTarget</t>
         </is>
       </c>
       <c r="B94" s="7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>放置格子：格子中心离跑道中心线小于这个距离就算跑道，不能放装置</t>
+          <t>挖矿：全网平均出块间隔（秒）</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>truckWet</t>
+          <t>blockReward</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>成就「浇透全场」：用洒水器累计淋湿多少名跑者后解锁洒水车（跨局累计，每名跑者只算一次）</t>
+          <t>挖矿：每个区块奖励的聪</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>scoreKill</t>
+          <t>adjustEvery</t>
         </is>
       </c>
       <c r="B96" s="7" t="n">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>分数：劝退率权重</t>
+          <t>挖矿：每多少个区块调整一次难度</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>scoreLives</t>
+          <t>netGrowth</t>
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>300</v>
+        <v>0.15</v>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>分数：剩余生命权重</t>
+          <t>挖矿：每次难度调整全网算力上涨比例</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
+          <t>freeNet</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>挖矿：经典模式的全网初始算力</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>rerollSats</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>区块奖励重抽一次花费的聪</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>padTrackGap</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>额外放置点：离跑道中心线的最小距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>padGap</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>额外放置点：离其他空位的最小距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>gridTrackGap</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>放置格子：格子中心离跑道中心线小于这个距离就算跑道，不能放装置</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>truckWet</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>成就「浇透全场」：用洒水器累计淋湿多少名跑者后解锁洒水车（跨局累计，每名跑者只算一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>scoreKill</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>分数：劝退率权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>scoreLives</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>分数：剩余生命权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
           <t>scoreClean</t>
         </is>
       </c>
-      <c r="B98" s="7" t="n">
+      <c r="B106" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>分数：无漏怪波数权重</t>
         </is>

--- a/config/blast-track-config.xlsx
+++ b/config/blast-track-config.xlsx
@@ -27116,7 +27116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -28646,73 +28646,88 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>gridTrackGap</t>
+          <t>truckTrackGap</t>
         </is>
       </c>
       <c r="B102" s="7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>放置格子：格子中心离跑道中心线小于这个距离就算跑道，不能放装置</t>
+          <t>洒水车：车底（整个车身着地的范围）离跑道中心线至少这么远；跑道半宽连路缘约 15，多出来的是留在车和跑道之间的草地</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>truckWet</t>
+          <t>gridTrackGap</t>
         </is>
       </c>
       <c r="B103" s="7" t="n">
-        <v>300</v>
+        <v>24</v>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>成就「浇透全场」：用洒水器累计淋湿多少名跑者后解锁洒水车（跨局累计，每名跑者只算一次）</t>
+          <t>放置格子：格子中心离跑道中心线小于这个距离就算跑道，不能放装置</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>scoreKill</t>
+          <t>truckWet</t>
         </is>
       </c>
       <c r="B104" s="7" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>分数：劝退率权重</t>
+          <t>成就「浇透全场」：用洒水器累计淋湿多少名跑者后解锁洒水车（跨局累计，每名跑者只算一次）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>scoreLives</t>
+          <t>scoreKill</t>
         </is>
       </c>
       <c r="B105" s="7" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>分数：剩余生命权重</t>
+          <t>分数：劝退率权重</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
+          <t>scoreLives</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>分数：剩余生命权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
           <t>scoreClean</t>
         </is>
       </c>
-      <c r="B106" s="7" t="n">
+      <c r="B107" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>分数：无漏怪波数权重</t>
         </is>
